--- a/data_extactor/batch/651_700.xlsx
+++ b/data_extactor/batch/651_700.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82500A5D-6EBA-410B-A49E-8E06F6243D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,1636 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="541">
+  <si>
+    <t>43-3061.00</t>
+  </si>
+  <si>
+    <t>Procurement Clerks</t>
+  </si>
+  <si>
+    <t>Buyer | Procurement Assistant | Procurement Officer | Procurement Specialist | Purchasing Assistant | Purchasing Associate | Purchasing Clerk | Purchasing Coordinator | Purchasing Specialist | Warehouse Clerk</t>
+  </si>
+  <si>
+    <t>Autotask | Electronic data interchange EDI software | IBM Maximo Asset Management | Intuit QuickBooks | Inventory tracking software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle Database | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Radiant Systems CounterPoint | SAP Business Objects | SAP software | Web browser software | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Speaking | Reading Comprehension | Active Listening | Critical Thinking | Writing | Monitoring | Active Learning | Mathematics</t>
+  </si>
+  <si>
+    <t>English Language | Administrative | Customer and Personal Service | Economics and Accounting | Administration and Management | Mathematics | Computers and Electronics | Transportation</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Near Vision | Written Expression | Information Ordering | Speech Clarity | Inductive Reasoning | Deductive Reasoning | Problem Sensitivity | Speech Recognition | Mathematical Reasoning | Category Flexibility</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Importance of Being Exact or Accurate | Contact With Others | Importance of Repeating Same Tasks | Frequency of Decision Making | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Spend Time Sitting | Impact of Decisions on Co-workers or Company Results | Indoors, Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Brokerage Clerks | Buyers and Purchasing Agents, Farm Products | Counter and Rental Clerks | Customer Service Representatives | Logisticians | Logistics Analysts | Office Clerks, General | Order Clerks | Postal Service Clerks | Production, Planning, and Expediting Clerks | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Purchasing Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Supply Chain Managers | Transportation, Storage, and Distribution Managers | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Compile information and records to draw up purchase orders for procurement of materials and services.</t>
+  </si>
+  <si>
+    <t>Approve and pay bills. | Calculate costs of orders, and charge or forward invoices to appropriate accounts. | Check shipments when they arrive to ensure that orders have been filled correctly and that goods meet specifications. | Compare prices, specifications, and delivery dates to determine the best bid among potential suppliers. | Compare suppliers' bills with bids and purchase orders to verify accuracy. | Contact suppliers to schedule or expedite deliveries and to resolve shortages, missed or late deliveries, and other problems. | Determine if inventory quantities are sufficient for needs, ordering more materials when necessary. | Locate suppliers, using sources such as catalogs and the internet, and interview them to gather information about products to be ordered. | Maintain knowledge of all organizational and governmental rules affecting purchases, and provide information about these rules to organization staff members and to vendors. | Monitor contractor performance, recommending contract modifications when necessary. | Monitor in-house inventory movement and complete inventory transfer forms for bookkeeping purposes. | Perform buying duties when necessary. | Prepare invitation-of-bid forms, and mail forms to supplier firms or distribute forms for public posting. | Prepare purchase orders and send copies to suppliers and to departments originating requests. | Prepare, maintain, and review purchasing files, reports and price lists. | Respond to customer and supplier inquiries about order status, changes, or cancellations. | Review requisition orders to verify accuracy, terminology, and specifications. | Track the status of requisitions, contracts, and orders. | Train and supervise subordinates and other staff.</t>
+  </si>
+  <si>
+    <t>43-3071.00</t>
+  </si>
+  <si>
+    <t>Tellers</t>
+  </si>
+  <si>
+    <t>Account Representative | Bank Teller | Branch Operations Specialist | Customer Relationship Specialist | Customer Service Associate (CSA) | Financial Services Representative (FSR) | Member Services Representative | Personal Banking Representative | Roving Teller | Teller</t>
+  </si>
+  <si>
+    <t>Email software | Hyland Software OnBase | IBM Notes | Information Technology Incorporated Premier Teller | Jack Henry &amp; Associates Vertex | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Sage 50 Accounting | Southern Data Systems TellerPro | Total Turnkey Solutions E-Vision</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Reading Comprehension | Monitoring | Mathematics | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Mathematics | Economics and Accounting | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Number Facility | Speech Recognition | Oral Expression | Speech Clarity | Problem Sensitivity | Information Ordering | Near Vision | Selective Attention | Written Comprehension | Written Expression | Mathematical Reasoning | Deductive Reasoning | Perceptual Speed | Category Flexibility | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Indoors, Environmentally Controlled | Spend Time Making Repetitive Motions | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Deal With External Customers or the Public in General | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Health and Safety of Other Workers | Spend Time Standing | Time Pressure</t>
+  </si>
+  <si>
+    <t>Accountants and Auditors | Bill and Account Collectors | Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Brokerage Clerks | Cashiers | Counter and Rental Clerks | Credit Analysts | Credit Authorizers, Checkers, and Clerks | Customer Service Representatives | Financial Managers | Gambling Cage Workers | Gambling Change Persons and Booth Cashiers | Loan Interviewers and Clerks | Loan Officers | New Accounts Clerks | Office Clerks, General | Payroll and Timekeeping Clerks | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Securities, Commodities, and Financial Services Sales Agents</t>
+  </si>
+  <si>
+    <t>Receive and pay out money. Keep records of money and negotiable instruments involved in a financial institution's various transactions.</t>
+  </si>
+  <si>
+    <t>Answer telephones and assist customers with their questions. | Arrange monies received in cash boxes and coin dispensers according to denomination. | Balance currency, coin, and checks in cash drawers at ends of shifts and calculate daily transactions, using computers, calculators, or adding machines. | Carry out special services for customers, such as ordering bank cards and checks. | Cash checks and pay out money after verifying that signatures are correct, that written and numerical amounts agree, and that accounts have sufficient funds. | Compose, type, and mail customer statements and other correspondence related to issues such as discrepancies and outstanding unpaid items. | Compute financial fees, interest, and service charges. | Count currency, coins, and checks received, by hand or using currency-counting machine, to prepare them for deposit or shipment to branch banks or the Federal Reserve Bank. | Count, verify, and post armored car deposits. | Enter customers' transactions into computers to record transactions and issue computer-generated receipts. | Examine checks for endorsements and to verify other information, such as dates, bank names, identification of the persons receiving payments, and the legality of the documents. | Explain, promote, or sell products or services, such as travelers' checks, savings bonds, money orders, and cashier's checks, using computerized information about customers to tailor recommendations. | Identify transaction mistakes when debits and credits do not balance. | Inform customers about foreign currency regulations and compute transaction fees for currency exchanges. | Issue checks to bond owners in settlement of transactions. | Monitor bank vaults to ensure cash balances are correct. | Obtain and process information required for the provision of services, such as opening accounts, savings plans, and purchasing bonds. | Order a supply of cash to meet daily needs. | Perform clerical tasks, such as typing, filing, and microfilm photography. | Prepare and verify cashier's checks. | Process and maintain records of customer loans. | Process transactions, such as term deposits, retirement savings plan contributions, automated teller transactions, night deposits, and mail deposits. | Quote unit exchange rates, following daily international rate sheets or computer displays. | Receive and count daily inventories of cash, drafts, and travelers' checks. | Receive checks and cash for deposit, verify amounts, and check accuracy of deposit slips. | Receive mortgage, loan, or public utility bill payments, verifying payment dates and amounts due. | Resolve problems or discrepancies concerning customers' accounts. | Sort and file deposit slips and checks.</t>
+  </si>
+  <si>
+    <t>43-3099.00</t>
+  </si>
+  <si>
+    <t>Financial Clerks, All Other</t>
+  </si>
+  <si>
+    <t>Accounting Clerk | Accounts Payable Clerk | Accounts Receivable Clerk | Audit Clerk | Finance Clerk | Financial Clerk | Fiscal Clerk | Reconciliation Clerk | Revenue Clerk | Settlement Clerk</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Email software | Microsoft Access | Microsoft SharePoint | Web browser software | Database software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat | SAP software | Enterprise resource planning ERP system</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Economics and Accounting | Mathematics | English Language | Customer and Personal Service | Computers and Electronics | Administration and Management | Law and Government</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Mathematical Reasoning | Number Facility | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Bookkeeping, Accounting, and Auditing Clerks | Billing and Posting Clerks | Bill and Account Collectors | Payroll and Timekeeping Clerks | Procurement Clerks | Tellers | Brokerage Clerks | New Accounts Clerks | Credit Authorizers, Checkers, and Clerks | Loan Interviewers and Clerks | Gambling Cage Workers | Insurance Claims and Policy Processing Clerks | Statistical Assistants | Data Entry Keyers | Office Clerks, General | Weighers, Measurers, Checkers, and Samplers, Recordkeeping | Accountants and Auditors | Budget Analysts | Financial Specialists, All Other | First-Line Supervisors of Office and Administrative Support Workers</t>
+  </si>
+  <si>
+    <t>All financial clerks not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform financial clerical duties in roles not classified separately. | Compile, verify, and post financial data to journals, ledgers, and systems. | Reconcile accounts, statements, and transaction records. | Process invoices, payments, receipts, and disbursements. | Verify the accuracy of figures, calculations, and supporting documentation. | Investigate and resolve discrepancies in financial records. | Prepare routine financial reports, summaries, and schedules. | Maintain filing systems for financial documents and correspondence. | Respond to inquiries from customers, vendors, and internal departments. | Operate accounting software, spreadsheets, and office equipment. | Comply with financial controls, retention policies, and audit requirements. | Assist with month-end and year-end closing procedures. | Monitor account balances and flag items requiring attention. | Prepare deposits and process incoming and outgoing funds.</t>
+  </si>
+  <si>
+    <t>43-4011.00</t>
+  </si>
+  <si>
+    <t>Brokerage Clerks</t>
+  </si>
+  <si>
+    <t>Account Administrator | Client Associate | Client Service Associate | Operations Clerk | Operations Coordinator | Registered Account Administrator | Registered Sales Assistant | Sales Assistant | Sales Trader | Trading Assistant</t>
+  </si>
+  <si>
+    <t>Account management software | Adobe Acrobat | Adobe Creative Cloud software | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Bloomberg Professional | HEAT Software GoldMine | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visual FoxPro | Microsoft Word | Online trading software | Oracle PeopleSoft | Royal Alliance VISION2020 Core | Salesforce software | Scheduling software | Structured query language SQL | Transaction processing software | Web browser software | WiredRed Software e/pop Basic</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring | Writing | Active Learning | Mathematics</t>
+  </si>
+  <si>
+    <t>English Language | Customer and Personal Service | Mathematics | Computers and Electronics | Economics and Accounting | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Near Vision | Written Expression | Speech Recognition | Speech Clarity | Information Ordering | Problem Sensitivity | Deductive Reasoning | Selective Attention | Number Facility | Mathematical Reasoning | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Contact With Others | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Spend Time Sitting | Determine Tasks, Priorities and Goals | Frequency of Decision Making | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Accountants and Auditors | Bill and Account Collectors | Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Credit Analysts | Credit Authorizers, Checkers, and Clerks | Customer Service Representatives | Financial Managers | Financial and Investment Analysts | Insurance Claims and Policy Processing Clerks | Loan Interviewers and Clerks | Loan Officers | Management Analysts | New Accounts Clerks | Office Clerks, General | Personal Financial Advisors | Procurement Clerks | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Securities, Commodities, and Financial Services Sales Agents | Tellers</t>
+  </si>
+  <si>
+    <t>Perform duties related to the purchase, sale, or holding of securities. Duties include writing orders for stock purchases or sales, computing transfer taxes, verifying stock transactions, accepting and delivering securities, tracking stock price fluctuations, computing equity, distributing dividends, and keeping records of daily transactions and holdings.</t>
+  </si>
+  <si>
+    <t>Compute total holdings, dividends, interest, transfer taxes, brokerage fees, or commissions and allocate appropriate payments to customers. | Correspond with customers and confer with coworkers to answer inquiries, discuss market fluctuations, or resolve account problems. | Document security transactions, such as purchases, sales, conversions, redemptions, or payments, using computers, accounting ledgers, or certificate records. | File, type, or operate standard office machines. | Monitor daily stock prices and compute fluctuations to determine the need for additional collateral to secure loans. | Perform clerical tasks, such as answering phones or distributing mail. | Prepare forms, such as receipts, withdrawal orders, transmittal papers, or transfer confirmations, based on transaction requests from stockholders. | Prepare reports summarizing daily transactions and earnings for individual customer accounts. | Schedule and coordinate transfer and delivery of security certificates between companies, departments, and customers. | Verify ownership and transaction information and dividend distribution instructions to ensure conformance with governmental regulations, using stock records and reports.</t>
+  </si>
+  <si>
+    <t>43-4021.00</t>
+  </si>
+  <si>
+    <t>Correspondence Clerks</t>
+  </si>
+  <si>
+    <t>Chargeback Specialist | Claims Correspondence Clerk | Correspondence Clerk | Correspondence Coordinator | Correspondence Representative (Correspondence Rep) | Correspondent | Dispute Resolution Analyst | Dispute Specialist | Office Technician (Office Tech) | Technical Clerk</t>
+  </si>
+  <si>
+    <t>Electronic data interchange EDI software | Electronic health record EHR software | Epic Systems | GE Healthcare Centricity EMR | Healthcare common procedure coding system HCPCS | Imaging software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Writing | Reading Comprehension | Active Listening | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Administrative | English Language | Customer and Personal Service | Economics and Accounting | Mathematics | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Written Expression | Written Comprehension | Oral Comprehension | Oral Expression | Near Vision | Speech Clarity | Problem Sensitivity | Deductive Reasoning | Information Ordering | Speech Recognition | Inductive Reasoning | Selective Attention | Category Flexibility | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>E-Mail | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Spend Time Sitting | Importance of Repeating Same Tasks | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Freedom to Make Decisions | Written Letters and Memos | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Time Pressure | Deal With External Customers or the Public in General | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Bill and Account Collectors | Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Court Reporters and Simultaneous Captioners | Court, Municipal, and License Clerks | Credit Authorizers, Checkers, and Clerks | Customer Service Representatives | Document Management Specialists | Eligibility Interviewers, Government Programs | Executive Secretaries and Executive Administrative Assistants | File Clerks | Insurance Claims and Policy Processing Clerks | Interviewers, Except Eligibility and Loan | Legal Secretaries and Administrative Assistants | Office Clerks, General | Payroll and Timekeeping Clerks | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Statistical Assistants</t>
+  </si>
+  <si>
+    <t>Compose letters or electronic correspondence in reply to requests for merchandise, damage claims, credit and other information, delinquent accounts, incorrect billings, or unsatisfactory services. Duties may include gathering data to formulate reply and preparing correspondence.</t>
+  </si>
+  <si>
+    <t>Compile data from records to prepare periodic reports. | Compile data pertinent to manufacture of special products for customers. | Complete form letters in response to requests or problems identified by correspondence. | Compose letters in reply to correspondence concerning such items as requests for merchandise, damage claims, credit information requests, delinquent accounts, incorrect billing, or unsatisfactory service. | Compute costs of records furnished to requesters, and write letters to obtain payment. | Confer with company personnel regarding feasibility of complying with writers' requests. | Ensure that money collected is properly recorded and secured. | Gather records pertinent to specific problems, review them for completeness and accuracy, and attach records to correspondence as necessary. | Maintain files and control records to show correspondence activities. | Prepare documents and correspondence, such as damage claims, credit and billing inquiries, invoices, and service complaints. | Prepare records for shipment by certified mail. | Present clear and concise explanations of governing rules and regulations. | Process orders for goods requested in correspondence. | Read incoming correspondence to ascertain nature of writers' concerns and to determine disposition of correspondence. | Review correspondence for format and typographical accuracy, assemble the information into a prescribed form with the correct number of copies, and submit it to an authorized official for signature. | Route correspondence to other departments for reply. | Type acknowledgment letters to persons sending correspondence.</t>
+  </si>
+  <si>
+    <t>43-4031.00</t>
+  </si>
+  <si>
+    <t>Court, Municipal, and License Clerks</t>
+  </si>
+  <si>
+    <t>City Clerk | City Recorder | Court Clerk | License Clerk | License Specialist | Motor Vehicle Field Representative (MVFR) | Motor Vehicle Licensing Clerk | Municipal Clerk | Permits Specialist | Town Clerk</t>
+  </si>
+  <si>
+    <t>Abilis CORIS Offender Management System | Adobe Acrobat | Corel WordPerfect Office Suite | Data Technologies Summit | Email software | IBM Judicial Enforcement Management System JEMS | IBM Notes | LexisNexis | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Spreadsheet applications | Syscon Court Clerk | Thomson Reuters Westlaw | Work scheduling software | Zoom</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Writing | Critical Thinking | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administrative | Law and Government | English Language | Administration and Management | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Near Vision | Written Comprehension | Speech Recognition | Speech Clarity | Information Ordering | Deductive Reasoning | Problem Sensitivity | Written Expression | Inductive Reasoning | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Written Letters and Memos | Spend Time Sitting | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Freedom to Make Decisions | Frequency of Decision Making | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Administrative Law Judges, Adjudicators, and Hearing Officers | Administrative Services Managers | Compliance Officers | Correspondence Clerks | Court Reporters and Simultaneous Captioners | Eligibility Interviewers, Government Programs | Executive Secretaries and Executive Administrative Assistants | File Clerks | First-Line Supervisors of Office and Administrative Support Workers | Insurance Claims and Policy Processing Clerks | Judges, Magistrate Judges, and Magistrates | Judicial Law Clerks | Lawyers | Legal Secretaries and Administrative Assistants | Office Clerks, General | Paralegals and Legal Assistants | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Tax Examiners and Collectors, and Revenue Agents | Title Examiners, Abstractors, and Searchers</t>
+  </si>
+  <si>
+    <t>Perform clerical duties for courts of law, municipalities, or governmental licensing agencies and bureaus. May prepare docket of cases to be called; secure information for judges and court; prepare draft agendas or bylaws for town or city council; answer official correspondence; keep fiscal records and accounts; issue licenses or permits; and record data, administer tests, or collect fees.</t>
+  </si>
+  <si>
+    <t>Answer inquiries from the general public regarding judicial procedures, court appearances, trial dates, adjournments, outstanding warrants, summonses, subpoenas, witness fees, or payment of fines. | Answer questions or provide advice to the public regarding licensing policies, procedures, or regulations. | Code information on license applications for entry into computers. | Coordinate or maintain office tracking systems for correspondence or follow-up actions. | Evaluate information on applications to verify completeness and accuracy and to determine whether applicants are qualified to obtain desired licenses. | Examine legal documents submitted to courts for adherence to laws or court procedures. | Instruct parties about timing of court appearances. | Issue public notification of all official activities or meetings. | Issue various permits and licenses, such as marriage, fishing, hunting, and dog licenses, and collect appropriate fees. | Participate in the administration of municipal elections, such as preparation or distribution of ballots, appointment or training of election officers, or tabulation or certification of results. | Perform administrative tasks, such as answering telephone calls, filing court documents, or maintaining office supplies or equipment. | Perform budgeting duties, such as assisting in budget preparation, expenditure review, or budget administration. | Perform contract administration duties, assisting with bid openings or the awarding of contracts. | Perform general office duties, such as taking or transcribing dictation, typing or proofreading correspondence, distributing or filing official forms, or scheduling appointments. | Perform record checks on past or current licensees, as required by investigations. | Plan or direct the maintenance, filing, safekeeping, or computerization of all municipal documents. | Prepare and issue orders of the court, such as probation orders, release documentation, sentencing information, or summonses. | Prepare dockets or calendars of cases to be called. | Prepare documents recording the outcomes of court proceedings. | Prepare meeting agendas or packets of related information. | Prepare ordinances, resolutions, or proclamations so that they can be executed, recorded, archived, or distributed. | Question applicants to obtain required information, such as name, address, or age, and record data on prescribed forms. | Record and edit the minutes of meetings and distribute to appropriate officials or staff members. | Record and maintain all vital and fiscal records and accounts. | Record case dispositions, court orders, or arrangements made for payment of court fees. | Research information in the municipal archives upon request of public officials or private citizens. | Respond to requests for information from the public, other municipalities, state officials, or state and federal legislative offices. | Search files and contact witnesses, attorneys, or litigants to obtain information for the court. | Train other workers or coordinate their work, as necessary. | Verify the authenticity of documents, such as foreign identification or immigration documents.</t>
+  </si>
+  <si>
+    <t>43-4041.00</t>
+  </si>
+  <si>
+    <t>Credit Authorizers, Checkers, and Clerks</t>
+  </si>
+  <si>
+    <t>Commercial Credit Reviewer | Commercial Loan Reviewer | Credit Investigator | Credit Processor | Credit Representative</t>
+  </si>
+  <si>
+    <t>Email software | Equifax software | Experian software | Financial accounting software | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | SAP software | Spreadsheet programs | Structured query language SQL | Tableau | Web browser software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Speaking | Active Listening | Critical Thinking | Writing | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Mathematics | Law and Government | Administrative | Economics and Accounting | Computers and Electronics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Oral Expression | Written Comprehension | Near Vision | Inductive Reasoning | Speech Recognition | Speech Clarity | Deductive Reasoning | Written Expression | Information Ordering</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | E-Mail | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Sitting | Time Pressure | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Written Letters and Memos | Freedom to Make Decisions | Importance of Repeating Same Tasks | Conflict Situations | Indoors, Environmentally Controlled | Spend Time Making Repetitive Motions | Dealing With Unpleasant, Angry, or Discourteous People | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Accountants and Auditors | Bill and Account Collectors | Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Brokerage Clerks | Correspondence Clerks | Credit Analysts | Credit Counselors | Customer Service Representatives | Eligibility Interviewers, Government Programs | Financial Examiners | Financial Managers | Insurance Claims and Policy Processing Clerks | Loan Interviewers and Clerks | Loan Officers | New Accounts Clerks | Personal Financial Advisors | Securities, Commodities, and Financial Services Sales Agents | Tax Examiners and Collectors, and Revenue Agents | Tellers</t>
+  </si>
+  <si>
+    <t>Authorize credit charges against customers' accounts. Investigate history and credit standing of individuals or business establishments applying for credit. May interview applicants to obtain personal and financial data, determine credit worthiness, process applications, and notify customers of acceptance or rejection of credit.</t>
+  </si>
+  <si>
+    <t>Call customers to collect payment on delinquent accounts. | Compile and analyze credit information gathered by investigation. | Consult with customers to resolve complaints or verify financial or credit transactions. | Contact former employers and other acquaintances to verify applicants' references, employment, health history, or social behavior. | Evaluate customers' computerized credit records and payment histories to decide whether to approve new credit, based on predetermined standards. | Examine city directories and public records to verify residence property ownership, bankruptcies, liens, arrest record, or unpaid taxes of applicants. | File sales slips in customers' ledgers for billing purposes. | Interview credit applicants by telephone or in person to obtain personal and financial data needed to complete credit report. | Keep records of customers' charges and payments. | Mail charge statements to customers. | Obtain information about potential creditors from banks, credit bureaus, and other credit services, and provide reciprocal information if requested. | Prepare credit cards or charge account plates. | Prepare reports of findings and recommendations. | Receive charge slips or credit applications by mail, or receive information from salespeople or merchants by telephone. | Relay credit report information to subscribers by mail or by telephone. | Review individual or commercial customer files to identify and select delinquent accounts for collection.</t>
+  </si>
+  <si>
+    <t>43-4051.00</t>
+  </si>
+  <si>
+    <t>Customer Service Representatives</t>
+  </si>
+  <si>
+    <t>Account Representative | Call Center Representative | Client Services Representative | Customer Care Representative (CCR) | Customer Service Agent | Customer Service Representative (CSR) | Customer Service Specialist | Customer Support Representative (Customer Support Rep) | Guest Service Agent | Member Services Representative (Member Services Rep)</t>
+  </si>
+  <si>
+    <t>ADP Workforce Now | AS/400 Database | Active Data Online WebChat | Adobe Acrobat | Adobe Creative Cloud software | Adobe Illustrator | Adobe Photoshop | Airtable | Apple Keynote | Apple macOS | Applied Systems Vision | Astute Solutions PowerCenter | Austin Logistics CallSelect | Austin Logistics CallTech | Austin Logistics Valeo | Avidian Technologies Prophet | Blackbaud The Raiser's Edge | Citrix cloud computing software | Customer account management software | Customer complaint ticketing management software | Customer service and support software | Customer service knowledge generation software | DSC Pacer Interactive Voice Response System | Data entry software | Database software | Delphi Technology | Dropbox | FaceTime | Facebook | FileMaker Pro | Fund accounting software | Google Docs | Google Drive | Google Meet | Google Sites | GroupMe | Handheld computer device software | Healthcare common procedure coding system HCPCS | Hosted Support ezSupport Pro | Human resource management software HRMS | IBM Cognos Impromptu | IBM Domino | IBM Notes | IBM Power Systems software | Intuit QuickBooks | Kronos Workforce Timekeeper | LexisNexis | LinkedIn | LogMeIn GoToMeeting | Lynk Everest | MEDITECH software | Main Street Softworks Monetra | McAfee | Medical condition coding software | Medical procedure coding software | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | Microsoft Office software | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Teams | Microsoft Windows | Microsoft Word | Multi-channel contact center software | Nearpod | NetSuite ERP | NortonLifeLock cybersecurity software | Open Text Fax Server, RightFax Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle Taleo | Padlet | Parature eRealtime | Parature eTicket | Poll Everywhere | SAP Business Objects | SAP Crystal Reports | SAP software | Sage 50 Accounting | Sage MAS 200 ERP | Sales force automation software | Salesforce software | Salesforce.com Salesforce CRM | ShoreTel | Skype | Slack | Social media sites | Stamps.com software | SugarSync | Tax software | Telemation e-CRM | Timpani Chat | Timpani Contact Center | Timpani Email | Unified messaging software | Virtual private networking VPN software | Voice over internet protocol VoIP system software | Yardi software | YouTube | Zoom | eStara Softphone | iShip | j2 Global Communications onebox</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Writing | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administration and Management | Sales and Marketing | Mathematics | Administrative | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Problem Sensitivity | Written Expression | Near Vision | Written Comprehension | Deductive Reasoning | Information Ordering | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Time Pressure | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | E-Mail | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Making Repetitive Motions | Work With or Contribute to a Work Group or Team | Spend Time Sitting | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Face-to-Face Discussions with Individuals and Within Teams | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Bill and Account Collectors | Billing and Posting Clerks | Brokerage Clerks | Cashiers | Correspondence Clerks | Counter and Rental Clerks | Credit Authorizers, Checkers, and Clerks | Eligibility Interviewers, Government Programs | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | Insurance Claims and Policy Processing Clerks | Insurance Sales Agents | Management Analysts | New Accounts Clerks | Office Clerks, General | Order Clerks | Receptionists and Information Clerks | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Telemarketers | Tellers</t>
+  </si>
+  <si>
+    <t>Interact with customers to provide basic or scripted information in response to routine inquiries about products and services. May handle and resolve general complaints. Excludes individuals whose duties are primarily installation, sales, repair, and technical support.</t>
+  </si>
+  <si>
+    <t>Check to ensure that appropriate changes were made to resolve customers' problems. | Compare disputed merchandise with original requisitions and information from invoices and prepare invoices for returned goods. | Complete contract forms, prepare change of address records, or issue service discontinuance orders, using computers. | Confer with customers by telephone or in person to provide information about products or services, take or enter orders, cancel accounts, or obtain details of complaints. | Contact customers to respond to inquiries or to notify them of claim investigation results or any planned adjustments. | Determine charges for services requested, collect deposits or payments, or arrange for billing. | Keep records of customer interactions or transactions, recording details of inquiries, complaints, or comments, as well as actions taken. | Obtain and examine all relevant information to assess validity of complaints and to determine possible causes, such as extreme weather conditions that could increase utility bills. | Recommend improvements in products, packaging, shipping, service, or billing methods and procedures to prevent future problems. | Refer unresolved customer grievances to designated departments for further investigation. | Resolve customers' service or billing complaints by performing activities such as exchanging merchandise, refunding money, or adjusting bills. | Review insurance policy terms to determine whether a particular loss is covered by insurance. | Solicit sales of new or additional services or products.</t>
+  </si>
+  <si>
+    <t>43-4061.00</t>
+  </si>
+  <si>
+    <t>Eligibility Interviewers, Government Programs</t>
+  </si>
+  <si>
+    <t>Benefits Program Tech (Benefits Program Technician) | Business and Employment Specialist | Case Manager | Eligibility Examiner | Eligibility Specialist | Eligibility Worker | Program Eligibility Specialist | Social Welfare Examiner (SWEX) | Workforce Advisor | Workforce Services Representative (WSR)</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat Reader | Client assessment software | Corel WinZip | Email software | GE Healthcare Centricity EMR | Google Meet | Medicaid management information system MMIS | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Resource and patient management system RPMS patient registration software | Resource and patient management system RPMS scheduling software | Web browser software | Zoom</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Writing | Critical Thinking | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administration and Management | Administrative | Personnel and Human Resources | Education and Training | Computers and Electronics | Mathematics | Law and Government | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Written Comprehension | Written Expression | Speech Clarity | Speech Recognition | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Category Flexibility</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Spend Time Sitting | Importance of Being Exact or Accurate | Contact With Others | Frequency of Decision Making | Importance of Repeating Same Tasks | Time Pressure | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Written Letters and Memos | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Child, Family, and School Social Workers | Claims Adjusters, Examiners, and Investigators | Compensation and Benefits Managers | Compensation, Benefits, and Job Analysis Specialists | Compliance Officers | Credit Authorizers, Checkers, and Clerks | Credit Counselors | Customer Service Representatives | Educational, Guidance, and Career Counselors and Advisors | Human Resources Assistants, Except Payroll and Timekeeping | Human Resources Specialists | Insurance Claims and Policy Processing Clerks | Interviewers, Except Eligibility and Loan | Legal Secretaries and Administrative Assistants | Management Analysts | Office Clerks, General | Patient Representatives | Rehabilitation Counselors | Social and Community Service Managers | Tax Examiners and Collectors, and Revenue Agents</t>
+  </si>
+  <si>
+    <t>Determine eligibility of persons applying to receive assistance from government programs and agency resources, such as welfare, unemployment benefits, social security, and public housing.</t>
+  </si>
+  <si>
+    <t>Answer applicants' questions about benefits and claim procedures. | Check with employers or other references to verify answers and obtain further information. | Compile, record, and evaluate personal and financial data to verify completeness and accuracy, and to determine eligibility status. | Compute and authorize amounts of assistance for programs, such as grants, monetary payments, and food stamps. | Conduct annual, interim, and special housing reviews and home visits to ensure conformance to regulations. | Initiate procedures to grant, modify, deny, or terminate assistance, or refer applicants to other agencies for assistance. | Interpret and explain information such as eligibility requirements, application details, payment methods, and applicants' legal rights. | Interview and investigate applicants for public assistance to gather information pertinent to their applications. | Interview benefits recipients at specified intervals to certify their eligibility for continuing benefits. | Investigate claimants for the possibility of fraud or abuse. | Keep records of assigned cases, and prepare required reports. | Monitor the payments of benefits throughout the duration of a claim. | Prepare applications and forms for applicants for such purposes as school enrollment, employment, and medical services. | Provide applicants with assistance in completing application forms, such as those for job referrals or unemployment compensation claims. | Provide social workers with pertinent information gathered during applicant interviews. | Refer applicants to job openings or to interviews with other staff, in accordance with administrative guidelines or office procedures. | Schedule benefits claimants for adjudication interviews to address questions of eligibility.</t>
+  </si>
+  <si>
+    <t>43-4071.00</t>
+  </si>
+  <si>
+    <t>File Clerks</t>
+  </si>
+  <si>
+    <t>Claims Clerk | Clerk | Clerk Typist | Documentation Specialist | File Clerk | Medical Records Clerk | Office Assistant | Police Records Clerk | Records Clerk | Records Custodian</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Electronic filing software | Electronic health record EHR software | Email software | Intuit QuickBooks | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Optical scanning software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Speaking | Writing | Monitoring | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Administrative | English Language | Customer and Personal Service | Law and Government | Computers and Electronics | Telecommunications | Mathematics | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Information Ordering | Written Comprehension | Category Flexibility | Near Vision | Oral Comprehension | Oral Expression | Written Expression | Selective Attention | Perceptual Speed | Speech Clarity | Speech Recognition | Deductive Reasoning | Flexibility of Closure | Inductive Reasoning | Problem Sensitivity | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | E-Mail | Spend Time Sitting | Importance of Being Exact or Accurate | Time Pressure | Work With or Contribute to a Work Group or Team | Importance of Repeating Same Tasks | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Archivists | Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Correspondence Clerks | Court Reporters and Simultaneous Captioners | Court, Municipal, and License Clerks | Data Entry Keyers | Document Management Specialists | Health Information Technologists and Medical Registrars | Management Analysts | Medical Records Specialists | Office Clerks, General | Payroll and Timekeeping Clerks | Postal Service Mail Sorters, Processors, and Processing Machine Operators | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Statistical Assistants | Title Examiners, Abstractors, and Searchers | Word Processors and Typists</t>
+  </si>
+  <si>
+    <t>File correspondence, cards, invoices, receipts, and other records in alphabetical or numerical order or according to the filing system used. Locate and remove material from file when requested.</t>
+  </si>
+  <si>
+    <t>Add new material to file records or create new records as necessary. | Answer questions about records or files. | Assign and record or stamp identification numbers or codes to index materials for filing. | Complete general financial activities, such as processing accounts payable, reviewing invoices, collecting cash payments, or issuing receipts. | Design forms related to filing systems. | Eliminate outdated or unnecessary materials, destroying them or transferring them to inactive storage, according to file maintenance guidelines or legal requirements. | Find, retrieve, and make copies of information from files in response to requests and deliver information to authorized users. | Gather materials to be filed from departments or employees. | Input data, such as file numbers, new or updated information, or document information codes into computer systems to support document and information retrieval. | Keep records of materials filed or removed, using logbooks or computers and generate computerized reports. | Modify or improve filing systems or implement new filing systems. | Operate mechanized files that rotate to bring needed records to a particular location. | Perform general office activities, such as typing, answering telephones, operating office machines, processing mail, or securing confidential materials. | Perform periodic inspections of materials or files to ensure correct placement, legibility, or proper condition. | Place materials into storage receptacles, such as file cabinets, boxes, bins, or drawers, according to classification and identification information. | Retrieve documents stored in microfilm or microfiche and place them in viewers for reading. | Scan or read incoming materials to determine how and where they should be classified or filed. | Sort or classify information according to guidelines, such as content, purpose, user criteria, or chronological, alphabetical, or numerical order. | Track materials removed from files to ensure that borrowed files are returned.</t>
+  </si>
+  <si>
+    <t>43-4081.00</t>
+  </si>
+  <si>
+    <t>Hotel, Motel, and Resort Desk Clerks</t>
+  </si>
+  <si>
+    <t>Desk Clerk | Front Desk Agent | Front Desk Associate | Front Desk Clerk | Front Office Agent | Guest Service Agent | Guest Service Representative | Guest Services Agent (GSA) | Night Auditor</t>
+  </si>
+  <si>
+    <t>ASI FrontDesk | Blink | Delphi Technology | Facebook | Incident tracking software | InnQuest roomMaster | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | Property management system PMS software | Ramesys Hospitality | Resort Data Processing | Yardi software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Monitoring | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Public Safety and Security | Administrative | Computers and Electronics | Administration and Management | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Category Flexibility | Information Ordering | Deductive Reasoning | Written Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Contact With Others | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | E-Mail | Indoors, Environmentally Controlled | Frequency of Decision Making | Dealing With Unpleasant, Angry, or Discourteous People | Freedom to Make Decisions | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Spend Time Standing | Importance of Repeating Same Tasks | Conflict Situations | Spend Time Making Repetitive Motions | Work Outcomes and Results of Other Workers | Written Letters and Memos | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Baggage Porters and Bellhops | Cashiers | Concierges | Counter and Rental Clerks | Customer Service Representatives | Dining Room and Cafeteria Attendants and Bartender Helpers | First-Line Supervisors of Housekeeping and Janitorial Workers | Food Servers, Nonrestaurant | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Locker Room, Coatroom, and Dressing Room Attendants | Lodging Managers | Maids and Housekeeping Cleaners | Medical Secretaries and Administrative Assistants | Office Clerks, General | Parking Attendants | Passenger Attendants | Receptionists and Information Clerks | Reservation and Transportation Ticket Agents and Travel Clerks | Ushers, Lobby Attendants, and Ticket Takers | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Accommodate hotel, motel, and resort patrons by registering and assigning rooms to guests, issuing room keys or cards, transmitting and receiving messages, keeping records of occupied rooms and guests' accounts, making and confirming reservations, and presenting statements to and collecting payments from departing guests.</t>
+  </si>
+  <si>
+    <t>Advise housekeeping staff when rooms have been vacated and are ready for cleaning. | Answer inquiries pertaining to hotel services, guest registration, and travel directions, or make recommendations regarding shopping, dining, or entertainment. | Arrange tours, taxis, or restaurant reservations for customers. | Clean and maintain lobby and common areas, such as restocking supplies and watering plants. | Compute bills, collect payments, and make change for guests. | Contact housekeeping or maintenance staff when guests report problems. | Date-stamp, sort, and rack incoming mail and messages. | Deposit guests' valuables in hotel safes or safe-deposit boxes. | Greet, register, and assign rooms to guests of hotels or motels. | Issue room keys and escort instructions to bellhops. | Keep records of room availability and guests' accounts, manually or using computers. | Make and confirm reservations. | Perform bookkeeping activities, such as balancing accounts and conducting nightly audits. | Plan, schedule or supervise the work of other employees. | Post charges, such as those for rooms, food, liquor, or telephone calls, to ledgers, manually or by using computers. | Prepare for basic food service, such as setting up continental breakfast or coffee and tea supplies. | Record guest comments or complaints, referring customers to managers as necessary. | Review accounts and charges with guests during the check out process. | Transmit and receive messages, using telephones or telephone switchboards. | Verify customers' credit, and establish how the customer will pay for the accommodation.</t>
+  </si>
+  <si>
+    <t>43-4111.00</t>
+  </si>
+  <si>
+    <t>Interviewers, Except Eligibility and Loan</t>
+  </si>
+  <si>
+    <t>Admissions Clerk | Admissions Representative | Admitting Representative | Data Collection Assistant | Interviewer | Market Research Interviewer | Registration Clerk | Research Interviewer | Survey Interviewer | Telephone Interviewer</t>
+  </si>
+  <si>
+    <t>Creative Research Systems The Survey System | Electronic health record EHR software | FileMaker Pro | FluidSurveys | Jenzabar EX | MEDITECH software | Medical condition coding software | Medical procedure coding software | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Teams | Microsoft Word | Nebu Dub InterViewer | Oracle PeopleSoft | Qualtrics Insight | RIVS automated interview software | SAP Business Objects | SaaS SurveyMonkey | Statistical software | Student information systems SIS software | Web browser software | Zoom</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administrative | Computers and Electronics | Mathematics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Recognition | Speech Clarity | Written Comprehension | Near Vision | Information Ordering | Written Expression | Problem Sensitivity | Deductive Reasoning | Inductive Reasoning | Selective Attention | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Contact With Others | E-Mail | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Spend Time Sitting | Deal With External Customers or the Public in General | Indoors, Environmentally Controlled | Time Pressure | Physical Proximity | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Making Repetitive Motions | Coordinate or Lead Others in Accomplishing Work Activities | Conflict Situations | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Work Outcomes and Results of Other Workers | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Correspondence Clerks | Customer Service Representatives | Eligibility Interviewers, Government Programs | File Clerks | First-Line Supervisors of Office and Administrative Support Workers | Health Information Technologists and Medical Registrars | Human Resources Assistants, Except Payroll and Timekeeping | Human Resources Specialists | Insurance Claims and Policy Processing Clerks | Management Analysts | Medical Records Specialists | Medical Secretaries and Administrative Assistants | Office Clerks, General | Patient Representatives | Payroll and Timekeeping Clerks | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Social Science Research Assistants | Statistical Assistants | Survey Researchers</t>
+  </si>
+  <si>
+    <t>Interview persons by telephone, mail, in person, or by other means for the purpose of completing forms, applications, or questionnaires. Ask specific questions, record answers, and assist persons with completing form. May sort, classify, and file forms.</t>
+  </si>
+  <si>
+    <t>Ask questions in accordance with instructions to obtain various specified information, such as person's name, address, age, religious preference, or state of residency. | Assist individuals in filling out applications or questionnaires. | Collect and analyze data, such as studying old records, tallying the number of outpatients entering each day or week, or participating in federal, state, or local population surveys as a Census Enumerator. | Compile, record, and code results or data from interview or survey, using computer or specified form. | Contact individuals to be interviewed at home, place of business, or field location, by telephone, mail, or in person. | Ensure payment for services by verifying benefits with the person's insurance provider or working out financing options. | Explain survey objectives and procedures to interviewees and interpret survey questions to help interviewees' comprehension. | Identify and report problems in obtaining valid data. | Identify and resolve inconsistencies in interviewees' responses by means of appropriate questioning or explanation. | Locate and list addresses and households. | Meet with supervisor daily to submit completed assignments and discuss progress. | Perform office duties, such as telemarketing or customer service inquiries, maintaining staff records, billing patients, or receiving payments. | Perform patient services, such as answering the telephone or assisting patients with financial or medical questions. | Prepare reports to provide answers in response to specific problems. | Review data obtained from interview for completeness and accuracy. | Supervise or train other staff members.</t>
+  </si>
+  <si>
+    <t>43-4121.00</t>
+  </si>
+  <si>
+    <t>Library Assistants, Clerical</t>
+  </si>
+  <si>
+    <t>Acquisitions Assistant | Cataloging Assistant | Library Aide | Library Assistant | Library Associate | Library Circulation Assistant | Library Clerical Assistant | Library Clerk | Library Services Assistant</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Adobe Photoshop | Automated circulation systems | C++ | Cataloging software | Database software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Windows | Microsoft Word | Online Computer Library Center (OCLC) databases | Recordkeeping software | ResourceMate Plus | Video retrieval systems | Web browser software | WorldCat</t>
+  </si>
+  <si>
+    <t>Active Listening | Reading Comprehension | Critical Thinking | Speaking | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administrative | English Language | Education and Training</t>
+  </si>
+  <si>
+    <t>Written Comprehension | Oral Expression | Information Ordering | Oral Comprehension | Near Vision | Problem Sensitivity | Speech Clarity | Speech Recognition | Selective Attention | Perceptual Speed | Category Flexibility | Written Expression</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Telephone Conversations | Contact With Others | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Frequency of Decision Making | Physical Proximity | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Spend Time Making Repetitive Motions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Archivists | Correspondence Clerks | Curators | Document Management Specialists | Editors | Elementary School Teachers, Except Special Education | Executive Secretaries and Executive Administrative Assistants | File Clerks | Instructional Coordinators | Librarians and Media Collections Specialists | Library Science Teachers, Postsecondary | Library Technicians | Management Analysts | Office Clerks, General | Office Machine Operators, Except Computer | Proofreaders and Copy Markers | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Social Science Research Assistants | Stockers and Order Fillers</t>
+  </si>
+  <si>
+    <t>Compile records, and sort, shelve, issue, and receive library materials such as books, electronic media, pictures, cards, slides and microfilm. Locate library materials for loan and replace material in shelving area, stacks, or files according to identification number and title. Register patrons to permit them to borrow books, periodicals, and other library materials.</t>
+  </si>
+  <si>
+    <t>Acquire books, pamphlets, periodicals, audio-visual materials, and other library supplies by checking prices, figuring costs, and preparing appropriate order forms and facilitating the ordering process by providing such information to others. | Answer routine inquiries and refer patrons in need of professional assistance to librarians. | Assist in the preparation of book displays. | Classify and catalog items according to content and purpose. | Deliver and retrieve items to and from departments by hand or using push carts. | Design or maintain library web site and online catalogues. | Enter and update patrons' records on computers. | Inspect returned books for condition and due-date status and compute any applicable fines. | Instruct patrons on how to use reference sources, card catalogs, and automated information systems. | Lend, reserve, and collect books, periodicals, videotapes, and other materials at circulation desks and process materials for inter-library loans. | Locate library materials for patrons, including books, periodicals, tape cassettes, Braille volumes, and pictures. | Maintain library equipment, such as photocopiers, scanners, and computers, and instruct patrons in proper use of such equipment. | Maintain records of items received, stored, issued, and returned and file catalog cards according to system used. | Manage reserve materials by placing items on reserve for library patrons, checking items in and out of library, and removing out-of-date items. | Open and close library during specified hours and secure library equipment, such as computers and audio-visual equipment. | Operate and maintain audio-visual equipment. | Operate small branch libraries, under the direction of off-site librarian supervisors. | Perform accounting and bookkeeping activities, such as invoicing, maintaining financial records, budgeting, and handling cash. | Perform clerical activities, such as answering phones, sorting mail, filing, typing, word processing, and photocopying and mailing out material. | Plan or participate in library events and programs, such as story time with children. | Prepare library statistics reports. | Prepare, store, and retrieve classification and catalog information, lecture notes, or other information related to stored documents, using computers. | Process new materials including books, audio-visual materials, and computer software. | Provide assistance to librarians in the maintenance of collections of books, periodicals, magazines, newspapers, and audio-visual and other materials. | Register new patrons and issue borrower identification cards that permit patrons to borrow books and other materials. | Repair books using mending tape, paste, and brushes or prepare books to be sent to a bindery for repair. | Review records, such as microfilm and issue cards, to identify titles of overdue materials and delinquent borrowers. | Schedule, supervise, and train clerical workers, volunteers, student assistants, and other library employees. | Select substitute titles when requested materials are unavailable, following criteria such as age, education, and interests. | Send out notices and accept fine payments for lost or overdue books. | Sort books, publications, and other items according to established procedure and return them to shelves, files, or other designated storage areas. | Take action to deal with disruptive or problem patrons.</t>
+  </si>
+  <si>
+    <t>43-4131.00</t>
+  </si>
+  <si>
+    <t>Loan Interviewers and Clerks</t>
+  </si>
+  <si>
+    <t>Closer | Licensed Loan Officer Assistant | Loan Analyst | Loan Clerk | Loan Closer | Loan Originator | Loan Processor | Mortgage Broker | Mortgage Loan Processor | Mortgage Processor</t>
+  </si>
+  <si>
+    <t>Automated financial software | Automated underwriting software | Credit reporting software | Encompass software | Fannie Mae Desktop Underwriter | Lending software systems | Loan tracking software | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Rockport Integrated Excel Underwriting | Software AG Underwriting Solution | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Writing | Active Learning | Mathematics | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administrative | Computers and Electronics | Law and Government | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Speech Recognition | Speech Clarity | Oral Expression | Problem Sensitivity | Information Ordering | Near Vision | Written Expression | Deductive Reasoning | Inductive Reasoning | Selective Attention | Mathematical Reasoning | Number Facility | Category Flexibility | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Spend Time Sitting | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Time Pressure | Written Letters and Memos | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | E-Mail | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Impact of Decisions on Co-workers or Company Results | Level of Competition | Coordinate or Lead Others in Accomplishing Work Activities | Dealing With Unpleasant, Angry, or Discourteous People | Conflict Situations | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Bill and Account Collectors | Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Brokerage Clerks | Credit Analysts | Credit Authorizers, Checkers, and Clerks | Credit Counselors | Eligibility Interviewers, Government Programs | Financial Examiners | Financial Managers | Insurance Claims and Policy Processing Clerks | Insurance Underwriters | Loan Officers | New Accounts Clerks | Personal Financial Advisors | Securities, Commodities, and Financial Services Sales Agents | Tax Examiners and Collectors, and Revenue Agents | Tax Preparers | Tellers | Title Examiners, Abstractors, and Searchers</t>
+  </si>
+  <si>
+    <t>Interview loan applicants to elicit information; investigate applicants' backgrounds and verify references; prepare loan request papers; and forward findings, reports, and documents to appraisal department. Review loan papers to ensure completeness, and complete transactions between loan establishment, borrowers, and sellers upon approval of loan.</t>
+  </si>
+  <si>
+    <t>Accept payment on accounts. | Answer questions and advise customers regarding loans and transactions. | Assemble and compile documents for loan closings, such as title abstracts, insurance forms, loan forms, and tax receipts. | Calculate, review, and correct errors on interest, principal, payment, and closing costs, using computers or calculators. | Check value of customer collateral to be held as loan security. | Contact credit bureaus, employers, and other sources to check applicants' credit and personal references. | Contact customers by mail, telephone, or in person concerning acceptance or rejection of applications. | Establish credit limits and grant extensions of credit on overdue accounts. | File and maintain loan records. | Interview loan applicants to obtain personal and financial data and to assist in completing applications. | Order property insurance or mortgage insurance policies to ensure protection against loss on mortgaged property. | Prepare and type loan applications, closing documents, legal documents, letters, forms, government notices, and checks, using computers. | Present loan and repayment schedules to customers. | Record applications for loan and credit, loan information, and disbursements of funds, using computers. | Review customer accounts to determine whether payments are made on time and that other loan terms are being followed. | Schedule and conduct closings of mortgage transactions. | Submit loan applications with recommendation for underwriting approval. | Verify and examine information and accuracy of loan application and closing documents.</t>
+  </si>
+  <si>
+    <t>43-4141.00</t>
+  </si>
+  <si>
+    <t>New Accounts Clerks</t>
+  </si>
+  <si>
+    <t>Banking Services Representative | Customer Service Specialist | Financial Service Representative | Financial Services Representative | Member Service Representative | New Accounts Clerk | New Accounts Representative | Personal Banker | Relationship Banker | Universal Banker</t>
+  </si>
+  <si>
+    <t>Corporate Information Factory CIF | DCI iCore | Email software | Financial needs analysis software | Fiserv financial services software | Harland Financial Solutions DepositPro | IBM Lotus Notes | IPS-Sendero Relationship Profitability Manager Catalyst | Microsoft Dynamics GP | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | Systems Union Group MIS DecisionWare | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | Administrative | English Language | Computers and Electronics | Mathematics | Economics and Accounting | Public Safety and Security | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Near Vision | Written Comprehension | Speech Recognition | Speech Clarity | Deductive Reasoning | Information Ordering | Inductive Reasoning | Problem Sensitivity | Mathematical Reasoning | Written Expression</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Time Pressure | Frequency of Decision Making | Physical Proximity | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Bill and Account Collectors | Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Brokerage Clerks | Credit Analysts | Credit Authorizers, Checkers, and Clerks | Credit Counselors | Customer Service Representatives | Financial Managers | Financial and Investment Analysts | Insurance Claims and Policy Processing Clerks | Insurance Sales Agents | Loan Interviewers and Clerks | Loan Officers | Office Clerks, General | Personal Financial Advisors | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Securities, Commodities, and Financial Services Sales Agents | Telemarketers | Tellers</t>
+  </si>
+  <si>
+    <t>Interview persons desiring to open accounts in financial institutions. Explain account services available to prospective customers and assist them in preparing applications.</t>
+  </si>
+  <si>
+    <t>Answer customers' questions and explain available services, such as deposit accounts, bonds, and securities. | Collect and record customer deposits and fees and issue receipts, using computers. | Compile information about new accounts, enter account information into computers, and file related forms or other documents. | Duplicate records for distribution to branch offices. | Execute wire transfers of funds. | Inform customers of procedures for applying for services, such as ATM cards, direct deposit of checks, and certificates of deposit. | Interview customers to obtain information needed for opening accounts or renting safe-deposit boxes. | Investigate and correct errors upon customers' request, according to customer and bank records. | Issue initial and replacement safe-deposit keys to customers, and admit customers to vaults. | Obtain credit records from reporting agencies. | Perform foreign currency transactions and sell traveler's checks. | Perform teller duties as required. | Process loan applications. | Refer customers to appropriate bank personnel to meet their financial needs. | Schedule repairs for locks on safe-deposit boxes.</t>
+  </si>
+  <si>
+    <t>43-4151.00</t>
+  </si>
+  <si>
+    <t>Order Clerks</t>
+  </si>
+  <si>
+    <t>Hub Associate | Materials Specialist | Order Analyst | Order Clerk | Order Entry Administrator (Order Entry Admin) | Order Entry Representative (Order Entry Rep) | Order Processing Clerk | Order Taker | Warehouse Clerk | Warehouse Person</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Apple Safari | Automated manifest system software | Corel WordPerfect Office Suite | Email software | IBM Sterling Configure, Price, Quote | Intuit QuickBooks | Inventory management systems | Microsoft Access | Microsoft Dynamics | Microsoft Edge | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft System Center | Microsoft Word | Mozilla Firefox | Oracle JD Edwards EnterpriseOne | Order management software | SAP software | Warehouse management system WMS | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Writing | Critical Thinking | Monitoring | Active Learning | Mathematics</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Production and Processing | Computers and Electronics | Education and Training | English Language | Administrative | Mathematics | Sales and Marketing | Transportation | Public Safety and Security | Personnel and Human Resources | Administration and Management | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Near Vision | Speech Recognition | Oral Comprehension | Oral Expression | Speech Clarity | Written Comprehension | Problem Sensitivity | Written Expression | Information Ordering | Inductive Reasoning | Deductive Reasoning | Perceptual Speed | Category Flexibility | Selective Attention | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Determine Tasks, Priorities and Goals | Contact With Others | Spend Time Sitting | Time Pressure | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Advertising Sales Agents | Billing and Posting Clerks | Cashiers | Correspondence Clerks | Counter and Rental Clerks | Customer Service Representatives | Driver/Sales Workers | First-Line Supervisors of Non-Retail Sales Workers | Mail Clerks and Mail Machine Operators, Except Postal Service | Office Clerks, General | Postal Service Clerks | Postmasters and Mail Superintendents | Procurement Clerks | Production, Planning, and Expediting Clerks | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Purchasing Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Receive and process incoming orders for materials, merchandise, classified ads, or services such as repairs, installations, or rental of facilities. Generally receives orders via mail, phone, fax, or other electronic means. Duties include informing customers of receipt, prices, shipping dates, and delays; preparing contracts; and handling complaints.</t>
+  </si>
+  <si>
+    <t>Adjust inventory records to reflect product movement. | Attempt to sell additional merchandise or services to prospective or current customers by telephone or through visits. | Calculate and compile order-related statistics, and prepare reports for management. | Check inventory records to determine availability of requested merchandise. | Collect payment for merchandise, record transactions, and send items, such as checks or money orders for further processing. | Compute total charges for merchandise or services and shipping charges. | Confer with production, sales, shipping, warehouse, or common carrier personnel to expedite or trace shipments. | Direct specified departments or units to prepare and ship orders to designated locations. | File copies of orders received, or post orders on records. | Inform customers by mail or telephone of order information, such as unit prices, shipping dates, and any anticipated delays. | Inspect outgoing work for compliance with customers' specifications. | Notify departments when supplies of specific items are low, or when orders would deplete available supplies. | Obtain customers' names, addresses, and billing information, product numbers, and specifications of items to be purchased, and enter this information on order forms. | Prepare invoices, shipping documents, and contracts. | Receive and respond to customer complaints. | Recommend merchandise or services that will meet customers' needs. | Recommend type of packing or labeling needed on order. | Review orders for completeness according to reporting procedures and forward incomplete orders for further processing. | Verify customer and order information for correctness, checking it against previously obtained information as necessary.</t>
+  </si>
+  <si>
+    <t>43-4161.00</t>
+  </si>
+  <si>
+    <t>Human Resources Assistants, Except Payroll and Timekeeping</t>
+  </si>
+  <si>
+    <t>Human Resources Administrative Assistant (HR Administrative Assistant) | Human Resources Assistant (HR Assistant) | Human Resources Associate (HR Associate) | Personnel Clerk</t>
+  </si>
+  <si>
+    <t>ADP Enterprise HR | ADP Workforce Now | Applicant tracking software | Blackboard Learn | Blackboard Learning System | Corel WordPerfect Office Suite | Database software | Document management system software | Email software | Employee performance management system | Employee self-service software | FileMaker Pro | Google Calendar | Google Docs | Human resource information system (HRIS) | Human resource management software HRMS | Learning management system LMS | LinkedIn | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Oracle HRIS | Oracle PeopleSoft | Oracle PeopleSoft Enterprise Employee Self-Service | Oracle PeopleSoft Enterprise Human Resources | Oracle Self-Service Human Resources | Oracle Taleo | SAP ERP | Scanning software | Ultimate Software UltiPro Workplace | Workscape HR Service Center</t>
+  </si>
+  <si>
+    <t>Active Listening | Reading Comprehension | Speaking | Writing | Monitoring | Critical Thinking | Active Learning</t>
+  </si>
+  <si>
+    <t>Personnel and Human Resources | Administrative | Customer and Personal Service | Administration and Management | English Language</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Written Expression | Speech Clarity | Near Vision | Speech Recognition | Problem Sensitivity | Deductive Reasoning | Information Ordering | Category Flexibility | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Contact With Others | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Importance of Repeating Same Tasks | Time Pressure | Spend Time Sitting | Determine Tasks, Priorities and Goals | Deal With External Customers or the Public in General | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Conflict Situations | Indoors, Environmentally Controlled | Impact of Decisions on Co-workers or Company Results | Written Letters and Memos | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Compensation and Benefits Managers | Compensation, Benefits, and Job Analysis Specialists | Eligibility Interviewers, Government Programs | Executive Secretaries and Executive Administrative Assistants | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | Health Information Technologists and Medical Registrars | Human Resources Managers | Human Resources Specialists | Interviewers, Except Eligibility and Loan | Labor Relations Specialists | Management Analysts | Medical Records Specialists | Medical Secretaries and Administrative Assistants | Office Clerks, General | Payroll and Timekeeping Clerks | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Social and Community Service Managers</t>
+  </si>
+  <si>
+    <t>Compile and keep personnel records. Record data for each employee, such as address, weekly earnings, absences, amount of sales or production, supervisory reports, and date of and reason for termination. May prepare reports for employment records, file employment records, or search employee files and furnish information to authorized persons.</t>
+  </si>
+  <si>
+    <t>Administer and score applicant and employee aptitude, personality, and interest assessment instruments. | Answer questions regarding examinations, eligibility, salaries, benefits, and other pertinent information. | Arrange for advertising or posting of job vacancies and notify eligible workers of position availability. | Arrange for in-house and external training activities. | Compile and prepare reports and documents pertaining to personnel activities. | Examine employee files to answer inquiries and provide information for personnel actions. | Explain company personnel policies, benefits, and procedures to employees or job applicants. | Gather personnel records from other departments or employees. | Inform job applicants of their acceptance or rejection of employment. | Interview job applicants to obtain and verify information used to screen and evaluate them. | Prepare and set up for new employee orientations. | Prepare badges, passes, and identification cards, and perform other security-related duties. | Process and review employment applications to evaluate qualifications or eligibility of applicants. | Process, verify, and maintain personnel related documentation, including staffing, recruitment, training, grievances, performance evaluations, classifications, and employee leaves of absence. | Provide assistance in administering employee benefit programs and worker's compensation plans. | Record data for each employee, including such information as addresses, weekly earnings, absences, amount of sales or production, supervisory reports on performance, and dates of and reasons for terminations. | Request information from law enforcement officials, previous employers, and other references to determine applicants' employment acceptability. | Search employee files to obtain information for authorized persons and organizations, such as credit bureaus and finance companies. | Select applicants meeting specified job requirements and refer them to hiring personnel.</t>
+  </si>
+  <si>
+    <t>43-4171.00</t>
+  </si>
+  <si>
+    <t>Receptionists and Information Clerks</t>
+  </si>
+  <si>
+    <t>Clerk Specialist | Front Desk Receptionist | Greeter | Information Assistant (Info Assistant) | Medical Receptionist | Member Services Representative (Member Services Rep) | Office Assistant | Receptionist | Registration Clerk | Scheduler</t>
+  </si>
+  <si>
+    <t>3M Post-it App | Alpha Software Alpha Five | Appointment scheduling software | Automated information system software | Billing software | Blackbaud The Raiser's Edge | Bookkeeping software | Claim processing system software | Corel WordPerfect Office Suite | Data entry software | Database software | Electronic calendar management software | Electronic health record EHR software | Email software | FileMaker Pro | Filing system software | GE Healthcare Centricity EMR | Google Docs | Google Drive | HMS | IBM Check Processing Control System CPSC | IBM Notes | Intrado SchoolMessenger | Intuit QuickBooks | Kodak Dental Systems Kodak SOFTDENT Practice management software PMS | McKesson Lytec | Medical condition coding software | Medical procedure coding software | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint Server | Microsoft Windows | Microsoft Word | St. Paul Travelers e-CARMA | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administrative | English Language | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Recognition | Speech Clarity | Written Comprehension | Written Expression | Near Vision | Selective Attention</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | Frequency of Decision Making | E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Impact of Decisions on Co-workers or Company Results | Work With or Contribute to a Work Group or Team | Spend Time Sitting | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions | Importance of Repeating Same Tasks | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Billing and Posting Clerks | Cashiers | Correspondence Clerks | Counter and Rental Clerks | Customer Service Representatives | Executive Secretaries and Executive Administrative Assistants | File Clerks | First-Line Supervisors of Office and Administrative Support Workers | Hotel, Motel, and Resort Desk Clerks | Interviewers, Except Eligibility and Loan | Legal Secretaries and Administrative Assistants | Medical Records Specialists | Medical Secretaries and Administrative Assistants | Office Clerks, General | Patient Representatives | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Switchboard Operators, Including Answering Service | Telemarketers</t>
+  </si>
+  <si>
+    <t>Answer inquiries and provide information to the general public, customers, visitors, and other interested parties regarding activities conducted at establishment and location of departments, offices, and employees within the organization.</t>
+  </si>
+  <si>
+    <t>Analyze data to determine answers to questions from customers or members of the public. | Calculate and quote rates for tours, stocks, insurance policies, or other products or services. | Collect, sort, distribute, or prepare mail, messages, or courier deliveries. | Enroll individuals to participate in programs and notify them of their acceptance. | File and maintain records. | Greet persons entering establishment, determine nature and purpose of visit, and direct or escort them to specific destinations. | Hear and resolve complaints from customers or the public. | Keep a current record of staff members' whereabouts and availability. | Operate telephone switchboard to answer, screen, or forward calls, providing information, taking messages, or scheduling appointments. | Perform administrative support tasks, such as proofreading, transcribing handwritten information, or operating calculators or computers to work with pay records, invoices, balance sheets, or other documents. | Perform duties, such as taking care of plants or straightening magazines to maintain lobby or reception area. | Process and prepare memos, correspondence, travel vouchers, or other documents. | Provide information about establishment, such as location of departments or offices, employees within the organization, or services provided. | Receive payment and record receipts for services. | Schedule appointments and maintain and update appointment calendars. | Schedule space or equipment for special programs and prepare lists of participants. | Take orders for merchandise or materials and send them to the proper departments to be filled. | Transmit information or documents to customers, using computer, mail, or facsimile machine.</t>
+  </si>
+  <si>
+    <t>43-4181.00</t>
+  </si>
+  <si>
+    <t>Reservation and Transportation Ticket Agents and Travel Clerks</t>
+  </si>
+  <si>
+    <t>Airline Ticket Agent | Airport Sales Agent | Customer Service Agent | Reservation Agent | Reservationist | Reservations Agent | Reservations and Ticketing Agent | Station Agent | Ticket Agent | Tour Sales Representative</t>
+  </si>
+  <si>
+    <t>Amadeus Altea Reservation | Computer reservation system CRS software | Corel WordPerfect Office Suite | Delphi Technology | Email software | Galileo 360 Fares | GuestServe | MICROS Systems MICROS 9700 HMS | MICROS Systems OPERA Property Management System PMS | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Property management system PMS software | Property scheduling software | Sabre Airline Solutions SabreSonic Ticket | Web browser software | Worldspan Go!</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Writing | Monitoring | Active Learning</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Computers and Electronics | Public Safety and Security | Transportation | Geography | Psychology</t>
+  </si>
+  <si>
+    <t>Oral Expression | Speech Recognition | Speech Clarity | Oral Comprehension | Written Comprehension | Information Ordering | Near Vision | Deductive Reasoning | Problem Sensitivity | Written Expression | Selective Attention | Category Flexibility | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Contact With Others | Importance of Repeating Same Tasks | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Time Pressure | Work With or Contribute to a Work Group or Team | Physical Proximity | Freedom to Make Decisions | Dealing With Unpleasant, Angry, or Discourteous People | Impact of Decisions on Co-workers or Company Results | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Conflict Situations | Degree of Automation | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Airfield Operations Specialists | Baggage Porters and Bellhops | Bus Drivers, Transit and Intercity | Cargo and Freight Agents | Concierges | Counter and Rental Clerks | Customer Service Representatives | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Passenger Attendants | Flight Attendants | Freight Forwarders | Hotel, Motel, and Resort Desk Clerks | Passenger Attendants | Receptionists and Information Clerks | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Shuttle Drivers and Chauffeurs | Transportation Security Screeners | Travel Agents | Travel Guides | Ushers, Lobby Attendants, and Ticket Takers</t>
+  </si>
+  <si>
+    <t>Make and confirm reservations for transportation or lodging, or sell transportation tickets. May check baggage and direct passengers to designated concourse, pier, or track; deliver tickets and contact individuals and groups to inform them of package tours; or provide tourists with travel or transportation information.</t>
+  </si>
+  <si>
+    <t>Announce arrival and departure information, using public address systems. | Answer inquiries regarding information, such as schedules, accommodations, procedures, or policies. | Assemble and issue required documentation, such as tickets, travel insurance policies, or itineraries. | Check baggage and cargo and direct passengers to designated locations for loading. | Confer with customers to determine their service requirements and travel preferences. | Contact customers or travel agents to advise them of travel conveyance changes or to confirm reservations. | Contact motel, hotel, resort, and travel operators to obtain current advertising literature. | Determine whether space is available on travel dates requested by customers, assigning requested spaces when available. | Examine passenger documentation to determine destinations and to assign boarding passes. | Inform clients of essential travel information, such as travel times, transportation connections, or medical and visa requirements. | Keep information facilities clean during operation. | Maintain computerized inventories of available passenger space and provide information on space reserved or available. | Make and confirm reservations for transportation and accommodations, using telephones, faxes, mail, and computers. | Open or close information facilities. | Plan routes, itineraries, and accommodation details, and compute fares and fees, using schedules, rate books, and computers. | Prepare customer invoices and accept payment. | Promote particular destinations, tour packages, and other travel services. | Provide boarding or disembarking assistance to passengers needing special assistance. | Provide clients with assistance in preparing required travel documents and forms. | Provide customers with travel suggestions and information sources, such as guides, directories, brochures, or maps. | Trace lost, delayed, or misdirected baggage for customers.</t>
+  </si>
+  <si>
+    <t>43-4199.00</t>
+  </si>
+  <si>
+    <t>Information and Record Clerks, All Other</t>
+  </si>
+  <si>
+    <t>Data Clerk | Document Clerk | Information Clerk | Records Clerk | Records Coordinator | Records Management Clerk | Records Specialist | Registration Clerk | Registry Clerk | Information Assistant</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Email software | Microsoft Access | Microsoft SharePoint | Web browser software | Database software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administration and Management | Computers and Electronics | Law and Government | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Perceptual Speed | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>File Clerks | Correspondence Clerks | Order Clerks | Receptionists and Information Clerks | Customer Service Representatives | Court, Municipal, and License Clerks | Eligibility Interviewers, Government Programs | Interviewers, Except Eligibility and Loan | Library Assistants, Clerical | Hotel, Motel, and Resort Desk Clerks | Human Resources Assistants, Except Payroll and Timekeeping | Reservation and Transportation Ticket Agents and Travel Clerks | Data Entry Keyers | Office Clerks, General | Medical Records Specialists | Document Management Specialists | Insurance Claims and Policy Processing Clerks | Statistical Assistants | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | First-Line Supervisors of Office and Administrative Support Workers</t>
+  </si>
+  <si>
+    <t>All information and record clerks not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform information and record clerk duties in roles not classified separately. | Create, index, file, and retrieve records in physical and electronic systems. | Verify the accuracy and completeness of submitted information and documents. | Enter and update data in databases, registries, and record systems. | Respond to requests for records and information from authorized parties. | Process applications, registrations, and routine transactions. | Maintain confidentiality and comply with records retention requirements. | Purge, archive, and dispose of records according to established schedules. | Prepare routine reports, logs, and statistical summaries. | Scan, convert, and quality-check documents for electronic storage. | Correct record errors and reconcile conflicting information. | Provide information and guidance to customers and staff about procedures. | Operate office equipment including scanners, copiers, and printers. | Monitor supplies and order materials for records operations.</t>
+  </si>
+  <si>
+    <t>43-5011.00</t>
+  </si>
+  <si>
+    <t>Cargo and Freight Agents</t>
+  </si>
+  <si>
+    <t>Air Export Specialist | Drop Shipment Clerk | Freight Broker | Intermodal Dispatcher | International Coordinator | Load Planner | Logistics Coordinator | Logistics Service Representative | Ship Broker | Traffic and Documentation Clerk</t>
+  </si>
+  <si>
+    <t>Brokerage software | Corel WordPerfect Office Suite | Database software | Email software | Microsoft Excel | Microsoft Office software | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Posting software | SAP software | Transportation management software | Transportation management system TMS software | Web browser software | Web-based dispatch software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Critical Thinking | Reading Comprehension | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Transportation | Geography | Public Safety and Security | English Language | Administration and Management | Education and Training | Law and Government | Telecommunications | Administrative | Customer and Personal Service | Communications and Media</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Written Comprehension | Near Vision | Problem Sensitivity | Written Expression | Speech Clarity | Speech Recognition | Selective Attention | Category Flexibility | Inductive Reasoning | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Contact With Others | Determine Tasks, Priorities and Goals | Spend Time Sitting | E-Mail | Freedom to Make Decisions | Time Pressure | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Dealing With Unpleasant, Angry, or Discourteous People | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | Couriers and Messengers | Customs Brokers | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | Freight Forwarders | Heavy and Tractor-Trailer Truck Drivers | Light Truck Drivers | Logisticians | Logistics Analysts | Order Clerks | Postal Service Clerks | Postal Service Mail Carriers | Postal Service Mail Sorters, Processors, and Processing Machine Operators | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Railroad Conductors and Yardmasters | Reservation and Transportation Ticket Agents and Travel Clerks | Shipping, Receiving, and Inventory Clerks | Transportation Inspectors | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Expedite and route movement of incoming and outgoing cargo and freight shipments in airline, train, and trucking terminals and shipping docks. Take orders from customers and arrange pickup of freight and cargo for delivery to loading platform. Prepare and examine bills of lading to determine shipping charges and tariffs.</t>
+  </si>
+  <si>
+    <t>Advise clients on transportation and payment methods. | Arrange insurance coverage for goods. | Assemble containers and crates used to transport items, such as machines or vehicles. | Attach address labels, identification codes, and shipping instructions to containers. | Check import or export documentation to determine cargo contents and use tariff coding system to classify goods according to fee or tariff group. | Contact vendors or claims adjustment departments to resolve shipment problems or contact service depots to arrange for repairs. | Coordinate and supervise activities of workers engaged in packing and shipping merchandise. | Determine method of shipment and prepare bills of lading, invoices, and other shipping documents. | Direct delivery trucks to shipping doors or designated marshaling areas and help load and unload goods safely. | Direct or participate in cargo loading to ensure completeness of load and even distribution of weight. | Enter shipping information into a computer by hand or by a hand-held scanner that reads bar codes on goods. | Estimate freight or postal rates and record shipment costs and weights. | Inspect and count items received and check them against invoices or other documents, recording shortages and rejecting damaged goods. | Install straps, braces, and padding to loads to prevent shifting or damage during shipment. | Keep records of all goods shipped, received, and stored. | Maintain a supply of packing materials. | Negotiate and arrange transport of goods with shipping or freight companies. | Notify consignees, passengers, or customers of freight or baggage arrival and arrange for delivery. | Open cargo containers and unwrap contents, using steel cutters, crowbars, or other hand tools. | Pack goods for shipping, using tools such as staplers, strapping machines, and hammers. | Prepare manifests showing numbers of airplane passengers and baggage, mail, and freight weights, transmitting data to destinations. | Retrieve stored items and trace lost shipments as necessary. | Route received goods to first available flight or to appropriate storage areas or departments, using forklifts, hand trucks, or other equipment. | Track delivery progress of shipments.</t>
+  </si>
+  <si>
+    <t>43-5011.01</t>
+  </si>
+  <si>
+    <t>Freight Forwarders</t>
+  </si>
+  <si>
+    <t>Air Export Agent | Air Export Coordinator | Export Coordinator | Freight Forwarder | GSA Coordinator (General Services Administration Coordinator) | Import Agent | Ocean Export Specialist | Relocation Coordinator | Route Specialist</t>
+  </si>
+  <si>
+    <t>AESDirect | Arcline ArcFreight | CEDAS Gateway | CargoWise ediEnterprise | Email software | IES Ecellerate | Kewill Global Trade and Logistics | Manufacturing resource planning MRP software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Oracle JD Edwards EnterpriseOne | Order management software | Package tracking software | QuestaWeb TradeMaster QW | RedBerry Logistics | Riege Software International Procars | SAP software | Star Tec Software Hercules Export | TMW Enterprise Transportation Management Systems | Tailwind Management Systems Tailwind | Web browser software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Active Listening | Critical Thinking | Speaking | Writing | Active Learning | Mathematics</t>
+  </si>
+  <si>
+    <t>Transportation | Administrative | Customer and Personal Service | Administration and Management | English Language | Computers and Electronics | Public Safety and Security | Geography | Personnel and Human Resources | Mathematics | Telecommunications | Economics and Accounting | Communications and Media | Law and Government | Production and Processing | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Information Ordering | Near Vision | Problem Sensitivity | Deductive Reasoning | Written Expression | Perceptual Speed | Flexibility of Closure | Number Facility | Category Flexibility | Inductive Reasoning | Speech Clarity | Speed of Closure | Mathematical Reasoning | Speech Recognition | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Time Pressure | Indoors, Environmentally Controlled | Contact With Others | Deal With External Customers or the Public in General | Spend Time Sitting | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Conflict Situations | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Level of Competition | Work Outcomes and Results of Other Workers | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | Buyers and Purchasing Agents, Farm Products | Cargo and Freight Agents | Couriers and Messengers | Customs Brokers | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | Light Truck Drivers | Logisticians | Logistics Analysts | Logistics Engineers | Postal Service Clerks | Postal Service Mail Carriers | Procurement Clerks | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Reservation and Transportation Ticket Agents and Travel Clerks | Shipping, Receiving, and Inventory Clerks | Transportation Inspectors | Transportation Planners | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Research rates, routings, or modes of transport for shipment of products. Maintain awareness of regulations affecting the international movement of cargo. Make arrangements for additional services, such as storage or inland transportation.</t>
+  </si>
+  <si>
+    <t>Analyze shipping routes to determine how to minimize environmental impact. | Arrange delivery or storage of goods at destinations. | Arrange for applicable duties, taxes, or paperwork for customs clearance. | Arrange for special transport of sensitive cargoes, such as livestock, food, or medical supplies. | Arrange for transport, using a variety of modes, such as rail, short sea shipping, air, or roadways, to minimize carbon emissions or other environmental impacts. | Assist clients in obtaining insurance reimbursements. | Calculate weight, volume, or cost of goods to be moved. | Complete customs paperwork. | Consider environmental sustainability factors when determining merchandise packing methods. | Consolidate loads with a common destination to reduce costs to individual shippers. | Determine efficient and cost-effective methods of moving goods from one location to another. | Inform clients of factors such as shipping options, timelines, transfers, or regulations affecting shipments. | Keep records of goods dispatched or received. | Maintain current knowledge of relevant legislation, political situations, or other factors that could affect freight shipping. | Make arrangements with customs brokers to facilitate the passage of goods through customs. | Monitor or record locations of goods in transit. | Negotiate shipping rates with freight carriers. | Obtain or arrange cargo insurance. | Pay or arrange for payment of freight or insurance fees or other charges. | Prepare invoices or cost quotations for freight transportation. | Prepare shipping documentation, such as bills of lading, packing lists, dock receipts, or certificates of origin. | Provide detailed port information to importers or exporters. | Provide shipment status notification to exporters, consignees, or insurers. | Recommend or arrange appropriate merchandise packing methods, according to climate, terrain, weight, nature of goods, or costs. | Recommend shipping solutions to minimize cost or environmental impacts. | Refer exporters to experts in areas such as trade financing, international marketing, government export requirements, international banking, or marine insurance. | Reserve necessary space on ships, aircraft, trains, or trucks. | Review the environmental records of freight carriers to inform shipping decisions. | Select shipment routes, based on nature of goods shipped, transit times, or security needs. | Verify adherence of documentation to customs, insurance, or regulatory requirements. | Verify proper packaging and labeling of exported goods.</t>
+  </si>
+  <si>
+    <t>43-5021.00</t>
+  </si>
+  <si>
+    <t>Couriers and Messengers</t>
+  </si>
+  <si>
+    <t>Courier | Driver | Laboratory Courier | Mail Carrier | Mailroom Courier | Messenger | Security Messenger | Transporter | Vehicle Delivery Worker</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Route mapping software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Critical Thinking | Writing | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Transportation | English Language</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Near Vision | Far Vision | Speech Recognition | Written Comprehension | Multilimb Coordination | Finger Dexterity | Manual Dexterity | Category Flexibility | Information Ordering | Problem Sensitivity | Written Expression | Speech Clarity | Depth Perception | Response Orientation | Control Precision | Arm-Hand Steadiness | Perceptual Speed | Inductive Reasoning | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Contact With Others | E-Mail | Spend Time Sitting | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | In an Enclosed Vehicle or Operate Enclosed Equipment | Indoors, Environmentally Controlled | Exposed to Disease or Infections | Exposed to Contaminants | Spend Time Making Repetitive Motions | Outdoors, Exposed to All Weather Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | Baggage Porters and Bellhops | Cargo and Freight Agents | Dispatchers, Except Police, Fire, and Ambulance | Driver/Sales Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | Freight Forwarders | Heavy and Tractor-Trailer Truck Drivers | Laborers and Freight, Stock, and Material Movers, Hand | Light Truck Drivers | Mail Clerks and Mail Machine Operators, Except Postal Service | Order Clerks | Postal Service Clerks | Postal Service Mail Carriers | Postal Service Mail Sorters, Processors, and Processing Machine Operators | Railroad Conductors and Yardmasters | Shipping, Receiving, and Inventory Clerks | Shuttle Drivers and Chauffeurs | Stockers and Order Fillers | Switchboard Operators, Including Answering Service</t>
+  </si>
+  <si>
+    <t>Pick up and deliver messages, documents, packages, and other items between offices or departments within an establishment or directly to other business concerns, traveling by foot, bicycle, motorcycle, automobile, or public conveyance.</t>
+  </si>
+  <si>
+    <t>Check with home offices after completed deliveries to confirm deliveries and collections and to receive instructions for other deliveries. | Collect, seal, and stamp outgoing mail, using postage meters and envelope sealers. | Deliver and pick up medical records, lab specimens, and medications to and from hospitals and other medical facilities. | Deliver messages and items, such as newspapers, documents, and packages, between establishment departments and to other establishments and private homes. | Load vehicles with listed goods, ensuring goods are loaded correctly and taking precautions with hazardous goods. | Obtain signatures and payments, or arrange for recipients to make payments. | Perform general office or clerical work, such as filing materials, operating duplicating machines, or running errands. | Perform routine maintenance on delivery vehicles, such as monitoring fluid levels and replenishing fuel. | Plan and follow the most efficient routes for delivering goods. | Receive messages or materials to be delivered, and information on recipients, such as names, addresses, telephone numbers, and delivery instructions, communicated via telephone, two-way radio, or in person. | Record information, such as items received and delivered and recipients' responses to messages. | Sort items to be delivered according to the delivery route. | Unload and sort items collected along delivery routes. | Use telephone to deliver verbal messages. | Walk, ride bicycles, drive vehicles, or use public conveyances to reach destinations to deliver messages or materials.</t>
+  </si>
+  <si>
+    <t>43-5031.00</t>
+  </si>
+  <si>
+    <t>Public Safety Telecommunicators</t>
+  </si>
+  <si>
+    <t>911 Dispatcher | Communications Officer | Communications Operator | Communications Specialist | Emergency Communications Dispatcher | Emergency Communications Operator (ECO) | Police Dispatcher | Public Safety Dispatcher | Telecommunicator</t>
+  </si>
+  <si>
+    <t>911 system information databases | Computer aided dispatch software | Corel WordPerfect Office Suite | Geographic information system GIS systems | Intrado SchoolMessenger | Law enforcement information databases | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | National Crime Information Center (NCIC) database | National Law Enforcement Telecommunications System NLETS | SAP software | Spillman Technologies Spillman Computer-Aided Dispatch | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Reading Comprehension | Active Learning | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Law and Government | English Language | Telecommunications | Customer and Personal Service | Geography | Communications and Media | Computers and Electronics | Administrative | Education and Training | Psychology | Personnel and Human Resources | Therapy and Counseling | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Speech Clarity | Problem Sensitivity | Speech Recognition | Selective Attention | Information Ordering | Written Comprehension | Deductive Reasoning | Inductive Reasoning | Time Sharing | Near Vision | Written Expression | Auditory Attention | Perceptual Speed | Flexibility of Closure | Speed of Closure | Category Flexibility | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Telephone Conversations | Spend Time Sitting | Contact With Others | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | E-Mail | Dealing With Unpleasant, Angry, or Discourteous People | Conflict Situations | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Freedom to Make Decisions | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Written Letters and Memos</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Airfield Operations Specialists | Ambulance Drivers and Attendants, Except Emergency Medical Technicians | Dispatchers, Except Police, Fire, and Ambulance | Emergency Management Directors | Emergency Medical Technicians | First-Line Supervisors of Firefighting and Prevention Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Police and Detectives | First-Line Supervisors of Security Workers | Forest Fire Inspectors and Prevention Specialists | Paramedics | Police and Sheriff's Patrol Officers | Railroad Conductors and Yardmasters | Security Guards | Security Management Specialists | Security Managers | Switchboard Operators, Including Answering Service | Telephone Operators | Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Operate telephone, radio, or other communication systems to receive and communicate requests for emergency assistance at 9-1-1 public safety answering points and emergency operations centers. Take information from the public and other sources regarding crimes, threats, disturbances, acts of terrorism, fires, medical emergencies, and other public safety matters. May coordinate and provide information to law enforcement and emergency response personnel. May access sensitive databases and other information sources as needed. May provide additional instructions to callers based on knowledge of and certification in law enforcement, fire, or emergency medical procedures.</t>
+  </si>
+  <si>
+    <t>Answer routine inquiries, and refer calls not requiring dispatches to appropriate departments and agencies. | Determine response requirements and relative priorities of situations, and dispatch units in accordance with established procedures. | Enter, update, and retrieve information from teletype networks and computerized data systems regarding such things as wanted persons, stolen property, vehicle registration, and stolen vehicles. | Learn material and pass required tests for certification. | Maintain access to, and security of, highly sensitive materials. | Maintain files of information relating to emergency calls, such as personnel rosters and emergency call-out and pager files. | Monitor alarm systems to detect emergencies, such as fires and illegal entry into establishments. | Monitor various radio frequencies, such as those used by public works departments, school security, and civil defense, to stay apprised of developing situations. | Observe alarm registers and scan maps to determine whether a specific emergency is in the dispatch service area. | Operate and maintain mobile dispatch vehicles and equipment. | Provide emergency medical instructions to callers. | Question callers to determine their locations and the nature of their problems to determine type of response needed. | Read and effectively interpret small-scale maps and information from a computer screen to determine locations and provide directions. | Receive incoming telephone or alarm system calls regarding emergency and non-emergency police and fire service, emergency ambulance service, information, and after-hours calls for departments within a city. | Record details of calls, dispatches, and messages. | Relay information and messages to and from emergency sites, to law enforcement agencies, and to all other individuals or groups requiring notification. | Scan status charts and computer screens, and contact emergency response field units to determine emergency units available for dispatch. | Test and adjust communication and alarm systems, and report malfunctions to maintenance units.</t>
+  </si>
+  <si>
+    <t>43-5032.00</t>
+  </si>
+  <si>
+    <t>Dispatchers, Except Police, Fire, and Ambulance</t>
+  </si>
+  <si>
+    <t>Aircraft Dispatcher | Charter Coordinator | City Dispatcher | Dispatcher (Dispatch) | Mine Dispatcher | Paratransit Dispatcher | School Bus Dispatcher | Taxi Dispatcher | Train Dispatcher | Truck Dispatcher</t>
+  </si>
+  <si>
+    <t>Air-Trak Cloudberry | Bornemann Associates Flight Plan | Command Alkon COMMANDconcrete | Computer aided dispatch software | Computer aided dispatching auto routing software | Database software | Digital Gateway e-automate | Dr. Dispatch | ESRI ArcIMS | Email software | Geomechanical design analysis GDA software | Global positioning system GPS software | Kronos Workforce Timekeeper | Locomotive distribution software | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Rail Traffic Track Warrant Control System | Resource management software | Routing software | SAP software | Sabre travel agent software | Scheduling software | Situation resource tracking software | TMW PowerSuite | Tangier Sky Scheduler View | Transportation management software | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Monitoring | Reading Comprehension | Writing | Critical Thinking | Active Learning</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Public Safety and Security | Administration and Management | Administrative | English Language | Transportation | Personnel and Human Resources | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Speech Recognition | Speech Clarity | Oral Comprehension | Oral Expression | Near Vision | Deductive Reasoning | Problem Sensitivity | Written Comprehension | Written Expression | Selective Attention | Information Ordering | Category Flexibility | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Frequency of Decision Making | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Work With or Contribute to a Work Group or Team | E-Mail | Importance of Being Exact or Accurate | Freedom to Make Decisions | Importance of Repeating Same Tasks | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers | Spend Time Sitting | Written Letters and Memos | Deal With External Customers or the Public in General | Conflict Situations | Spend Time Making Repetitive Motions | Indoors, Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Aircraft Cargo Handling Supervisors | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | Heavy and Tractor-Trailer Truck Drivers | Laborers and Freight, Stock, and Material Movers, Hand | Light Truck Drivers | Locomotive Engineers | Postmasters and Mail Superintendents | Power Distributors and Dispatchers | Production, Planning, and Expediting Clerks | Public Safety Telecommunicators | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Conductors and Yardmasters | Shipping, Receiving, and Inventory Clerks | Shuttle Drivers and Chauffeurs | Switchboard Operators, Including Answering Service | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Schedule and dispatch workers, work crews, equipment, or service vehicles for conveyance of materials, freight, or passengers, or for normal installation, service, or emergency repairs rendered outside the place of business. Duties may include using radio, telephone, or computer to transmit assignments and compiling statistics and reports on work progress.</t>
+  </si>
+  <si>
+    <t>Advise personnel about traffic problems, such as construction areas, accidents, congestion, weather conditions, or other hazards. | Arrange for necessary repairs to restore service and schedules. | Confer with customers or supervising personnel to address questions, problems, or requests for service or equipment. | Determine types or amounts of equipment, vehicles, materials, or personnel required, according to work orders or specifications. | Monitor personnel or equipment locations and utilization to coordinate service and schedules. | Order supplies or equipment and issue them to personnel. | Oversee all communications within specifically assigned territories. | Prepare daily work and run schedules. | Receive or prepare work orders. | Record and maintain files or records of customer requests, work or services performed, charges, expenses, inventory, or other dispatch information. | Relay work orders, messages, or information to or from work crews, supervisors, or field inspectors, using telephones or two-way radios. | Schedule or dispatch workers, work crews, equipment, or service vehicles to appropriate locations, according to customer requests, specifications, or needs, using radios or telephones.</t>
+  </si>
+  <si>
+    <t>43-5041.00</t>
+  </si>
+  <si>
+    <t>Meter Readers, Utilities</t>
+  </si>
+  <si>
+    <t>Field Technician | Fieldman | Meter Reader | Meter Reader Inspector | Meter Reading Clerk | Meter Technician | Utility Service Worker | Water Inspector | Water Meter Reader | Water Use Inspector</t>
+  </si>
+  <si>
+    <t>Billing software | Geographic information system GIS systems | Graphing software | Mapping software | Meter reading software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Supervisory control and data acquisition SCADA software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Public Safety and Security | English Language | Mathematics</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Comprehension | Oral Expression | Trunk Strength | Perceptual Speed | Information Ordering | Speech Clarity | Speech Recognition | Far Vision | Extent Flexibility | Multilimb Coordination | Control Precision | Arm-Hand Steadiness | Problem Sensitivity | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | In an Enclosed Vehicle or Operate Enclosed Equipment | Importance of Being Exact or Accurate | Exposed to Contaminants | Spend Time Making Repetitive Motions | Deal With External Customers or the Public in General | Exposed to Extremely Bright or Inadequate Lighting Conditions | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Work With or Contribute to a Work Group or Team | Importance of Repeating Same Tasks | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Frequency of Decision Making | Freedom to Make Decisions | Spend Time Bending or Twisting Your Body | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Telephone Conversations | Contact With Others | Spend Time Walking or Running | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Exposed to Hazardous Equipment | Exposed to Cramped Work Space, Awkward Positions</t>
+  </si>
+  <si>
+    <t>Calibration Technologists and Technicians | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical Power-Line Installers and Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Gas Plant Operators | Geothermal Technicians | Inspectors, Testers, Sorters, Samplers, and Weighers | Maintenance and Repair Workers, General | Plumbers, Pipefitters, and Steamfitters | Power Distributors and Dispatchers | Power Plant Operators | Pump Operators, Except Wellhead Pumpers | Septic Tank Servicers and Sewer Pipe Cleaners | Stationary Engineers and Boiler Operators | Telecommunications Equipment Installers and Repairers, Except Line Installers | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Read meter and record consumption of electricity, gas, water, or steam.</t>
+  </si>
+  <si>
+    <t>Answer customers' questions about services and charges, or direct them to customer service centers. | Connect and disconnect utility services at specific locations. | Inspect meters for unauthorized connections, defects, and damage, such as broken seals. | Leave messages to arrange different times to read meters in cases in which meters are not accessible. | Perform preventative maintenance or minor repairs on meters. | Read electric, gas, water, or steam consumption meters and enter data in route books or hand-held computers. | Report lost or broken keys. | Report to service departments any problems, such as meter irregularities, damaged equipment, or impediments to meter access, including dogs. | Update client address and meter location information. | Upload into office computers all information collected on hand-held computers during meter rounds, or return route books or hand-held computers to business offices so that data can be compiled. | Verify readings in cases where consumption appears to be abnormal, and record possible reasons for fluctuations. | Walk or drive vehicles along established routes to take readings of meter dials.</t>
+  </si>
+  <si>
+    <t>43-5051.00</t>
+  </si>
+  <si>
+    <t>Postal Service Clerks</t>
+  </si>
+  <si>
+    <t>Bulk Mail Technician | Clerk | Distribution Clerk | Part Time Flexible Clerk (PTF Clerk) | Postal Clerk | Sales and Distribution Clerk | Sales and Service Associate (SSA) | Window Clerk</t>
+  </si>
+  <si>
+    <t>Budgeting software | Delivery operations information system DOIS | Electronic Time Clock ETC | Inventory tracking software | Microsoft Windows | NCR Advanced Store | Time and Attendance Collection System TACS</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Monitoring | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Mathematics | Sales and Marketing | Administrative | Computers and Electronics | Transportation</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Near Vision | Speech Clarity | Speech Recognition | Written Comprehension | Trunk Strength | Manual Dexterity | Category Flexibility | Information Ordering | Deductive Reasoning | Finger Dexterity | Arm-Hand Steadiness | Selective Attention | Perceptual Speed | Number Facility | Mathematical Reasoning | Inductive Reasoning | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Contact With Others | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Spend Time Standing | Physical Proximity | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Dealing With Unpleasant, Angry, or Discourteous People | Importance of Repeating Same Tasks | Telephone Conversations | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Billing and Posting Clerks | Cargo and Freight Agents | Cashiers | Counter and Rental Clerks | Couriers and Messengers | File Clerks | Freight Forwarders | Light Truck Drivers | Mail Clerks and Mail Machine Operators, Except Postal Service | Office Clerks, General | Order Clerks | Postal Service Mail Carriers | Postal Service Mail Sorters, Processors, and Processing Machine Operators | Postmasters and Mail Superintendents | Procurement Clerks | Production, Planning, and Expediting Clerks | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Switchboard Operators, Including Answering Service | Tellers</t>
+  </si>
+  <si>
+    <t>Perform any combination of tasks in a United States Postal Service (USPS) post office, such as receive letters and parcels; sell postage and revenue stamps, postal cards, and stamped envelopes; fill out and sell money orders; place mail in pigeon holes of mail rack or in bags; and examine mail for correct postage. Includes postal service clerks employed by USPS contractors.</t>
+  </si>
+  <si>
+    <t>Answer questions regarding mail regulations and procedures, postage rates, and post office boxes. | Cash money orders. | Check mail to ensure correct postage and that packages and letters are in proper condition for mailing. | Complete forms regarding changes of address, or theft or loss of mail, or for special services such as registered or priority mail. | Feed mail into postage canceling devices or hand stamp mail to cancel postage. | Keep money drawers in order, and record and balance daily transactions. | Obtain signatures from recipients of registered or special delivery mail. | Order retail items and other supplies for office use. | Provide assistance to the public in complying with federal regulations of Postal Service and other federal agencies. | Provide customers with assistance in filing claims for mail theft, or lost or damaged mail. | Put undelivered parcels away, retrieve them when customers come to claim them, and complete any related documentation. | Receive letters and parcels, and place mail into bags. | Register, certify, and insure letters and parcels. | Rent post office boxes to customers. | Respond to complaints regarding mail theft, delivery problems, and lost or damaged mail, filling out forms and making appropriate referrals for investigation. | Sell and collect payment for products such as stamps, prepaid mail envelopes, and money orders. | Sort incoming and outgoing mail, according to type and destination, by hand or by operating electronic mail-sorting and scanning devices. | Transport mail from one work station to another. | Weigh letters and parcels, compute mailing costs based on type, weight, and destination, and affix correct postage.</t>
+  </si>
+  <si>
+    <t>43-5052.00</t>
+  </si>
+  <si>
+    <t>Postal Service Mail Carriers</t>
+  </si>
+  <si>
+    <t>City Carrier | City Carrier Assistant (CCA) | City Letter Carrier | City Mail Carrier | Letter Carrier | Mail Carrier | Rural Carrier | Rural Carrier Associate (RCA) | Rural Mail Carrier | Rural Route Carrier</t>
+  </si>
+  <si>
+    <t>Address Management System AMS | Automated Data Collection System ADCS | Delivery Routing System DRS | Delivery operations information system DOIS | Electronic Time Clock ETC | End of Run Report EOR | Microsoft Office software | Microsoft Windows | Microsoft Word | Time and Attendance Collection System TACS</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Public Safety and Security | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Information Ordering | Near Vision | Speech Clarity | Speech Recognition | Trunk Strength | Arm-Hand Steadiness | Category Flexibility | Problem Sensitivity | Written Comprehension | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Making Repetitive Motions | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Indoors, Environmentally Controlled | Exposed to Very Hot or Cold Temperatures | Deal With External Customers or the Public in General | Frequency of Decision Making | Contact With Others | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Baggage Porters and Bellhops | Cargo and Freight Agents | Counter and Rental Clerks | Couriers and Messengers | Customer Service Representatives | Dispatchers, Except Police, Fire, and Ambulance | Driver/Sales Workers | Freight Forwarders | Light Truck Drivers | Mail Clerks and Mail Machine Operators, Except Postal Service | Office Clerks, General | Order Clerks | Postal Service Clerks | Postal Service Mail Sorters, Processors, and Processing Machine Operators | Postmasters and Mail Superintendents | Reservation and Transportation Ticket Agents and Travel Clerks | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Switchboard Operators, Including Answering Service | Transportation, Storage, and Distribution Managers</t>
+  </si>
+  <si>
+    <t>Sort and deliver mail for the United States Postal Service (USPS). Deliver mail on established route by vehicle or on foot. Includes postal service mail carriers employed by USPS contractors.</t>
+  </si>
+  <si>
+    <t>Answer customers' questions about postal services and regulations. | Bundle mail in preparation for delivery or transportation to relay boxes. | Complete forms that notify publishers of address changes. | Deliver mail to residences and business establishments along specified routes by walking or driving, using a combination of satchels, carts, cars, and small trucks. | Hold mail for customers who are away from delivery locations. | Leave notices telling patrons where to collect mail that could not be delivered. | Maintain accurate records of deliveries. | Meet schedules for the collection and return of mail. | Obtain signed receipts for registered, certified, and insured mail, collect associated charges, and complete any necessary paperwork. | Provide customers with change of address cards and other forms. | Record address changes and redirect mail for those addresses. | Register, certify, and insure parcels and letters. | Report any unusual circumstances concerning mail delivery, including the condition of street letter boxes. | Return incorrectly addressed mail to senders. | Return to the post office with mail collected from homes, businesses, and public mailboxes. | Scan labels on letters or parcels to confirm receipt. | Sell stamps and money orders. | Sign for cash-on-delivery and registered mail before leaving the post office. | Sort mail for delivery, arranging it in delivery sequence. | Travel to post offices to pick up the mail for routes or pick up mail from postal relay boxes. | Turn in money and receipts collected along mail routes.</t>
+  </si>
+  <si>
+    <t>43-5053.00</t>
+  </si>
+  <si>
+    <t>Postal Service Mail Sorters, Processors, and Processing Machine Operators</t>
+  </si>
+  <si>
+    <t>Automation Clerk | Computer Forwarding System Markup Clerk (CFS Markup Clerk) | Distribution Clerk | Flat Sorting Machine Clerk (FSM Clerk) | Mail Handler | Mail Handler Equipment Operator | Mail Processing Clerk | Mail Processor | Parcel Post Distribution Machine Operator (PDPMO) | Small Package and Bundle Sorter Clerk (SPBS Clerk)</t>
+  </si>
+  <si>
+    <t>Address Management System AMS | Automated Package Processing System APPS | Barcode reader software | Delivery Routing System DRS | Delivery operations information system DOIS | Directory software | Electronic Time Clock ETC | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft SharePoint | Microsoft Word | Multi-line optical character reader OCR software | NCR Advanced Store | SAP software | Teradata Database | Time and Attendance Collection System TACS</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Manual Dexterity | Static Strength | Multilimb Coordination | Perceptual Speed | Category Flexibility | Information Ordering | Written Comprehension | Speech Clarity | Speech Recognition | Trunk Strength | Finger Dexterity | Deductive Reasoning | Problem Sensitivity | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Time Pressure | Spend Time Making Repetitive Motions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Pace Determined by Speed of Equipment | Contact With Others | Spend Time Walking or Running | Degree of Automation | Spend Time Bending or Twisting Your Body | Importance of Repeating Same Tasks | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Cargo and Freight Agents | Conveyor Operators and Tenders | Couriers and Messengers | Data Entry Keyers | File Clerks | Laborers and Freight, Stock, and Material Movers, Hand | Machine Feeders and Offbearers | Mail Clerks and Mail Machine Operators, Except Postal Service | Office Clerks, General | Office Machine Operators, Except Computer | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Postal Service Clerks | Postal Service Mail Carriers | Postmasters and Mail Superintendents | Production, Planning, and Expediting Clerks | Recycling and Reclamation Workers | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Weighers, Measurers, Checkers, and Samplers, Recordkeeping</t>
+  </si>
+  <si>
+    <t>Prepare incoming and outgoing mail for distribution for the United States Postal Service (USPS). Examine, sort, and route mail. Load, operate, and occasionally adjust and repair mail processing, sorting, and canceling machinery. Keep records of shipments, pouches, and sacks, and perform other duties related to mail handling within the postal service. Includes postal service mail sorters and processors employed by USPS contractors.</t>
+  </si>
+  <si>
+    <t>Bundle, label, and route sorted mail to designated areas, depending on destinations and according to established procedures and deadlines. | Cancel letter or parcel post stamps by hand. | Check items to ensure that addresses are legible and correct, that sufficient postage has been paid or the appropriate documentation is attached, and that items are in a suitable condition for processing. | Clear jams in sorting equipment. | Direct items according to established routing schemes, using computer-controlled keyboards or voice-recognition equipment. | Distribute incoming mail into the correct boxes or pigeonholes. | Load and unload mail trucks, sometimes lifting containers of mail onto equipment that transports items to sorting stations. | Move containers of mail, using equipment, such as forklifts and automated "trains". | Open and label mail containers. | Operate various types of equipment, such as computer scanning equipment, addressographs, mimeographs, optical character readers, and bar-code sorters. | Rewrap soiled or broken parcels. | Search directories to find correct addresses for redirected mail. | Sort odd-sized mail by hand, sort mail that other workers have been unable to sort, and segregate items requiring special handling. | Train new workers.</t>
+  </si>
+  <si>
+    <t>43-5061.00</t>
+  </si>
+  <si>
+    <t>Production, Planning, and Expediting Clerks</t>
+  </si>
+  <si>
+    <t>Expeditor | Inventory Control Specialist | Material Requirements Planner (MRP) | Materials Coordinator | Materials Planner | Production Assistant | Production Clerk | Production Controller | Production Planner | Production Scheduler</t>
+  </si>
+  <si>
+    <t>ABB Production Planning | ADi SmartBOL | Accvision ABMIS | Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Aestiva Purchase Order | Airtable | Applied Software Technologies Asset Maintenance and Materials Management System | Asprova | Bill of lading software | Bills of lading software | Cost estimating software | Creo Synapse Upfront | DM2 Bills of Lading | Data entry software | Database software | ERP INDUSTRIOS Material Planning | Enterprise Logix | Epicor Vantage ERP | Exact MAX | Exact Software Macola ES | Factory Edge MRP | FileMaker Pro | Fund accounting software | Geac MPC Production | Giraffe Production Systems Giraffe Schedule System | Google Docs | Google Drive | Honeywell Wintress PACNet | IBM Notes | Inetsoft | Ingenious ProPlan | Ingenious ProSched | InteProc Material Requirements Planning | Interwave Technology RS Bizware Scheduler | Intuit QuickBooks | KAPES | LSA Visual DBR | LSA Visual Easy Lean | Lamar Info Net | MEDITECH software | MTI Systems Costimator JS | Made2Manage Supply Chain Management | Maynard PlanStaff Manager | Medical condition coding software | Medical procedure coding software | Micro Estimating FabPlan | MicroStrategy Report Services | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics ERP | Microsoft Dynamics GP | Microsoft Excel | Microsoft Office software | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | NetSuite ERP | Niku Clarity | Oracle Database | Oracle Flow Manufacturing | Oracle JD Edwards EnterpriseOne | Oracle Manufacturing Scheduling | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera Systems | PMC KanbanSIM | PRONTO Xi | Pelion manufacturing process optimization MPO software | Pivotal Z Prestige Scheduler | Preactor APS | Preactor Finite Capacity Scheduling | Production scheduling and planning software | QAD Adaptive ERP | Questek Humanis | RSS Solutions NaView | Rytech Software Small Business Inventory Control | SAP Crystal Reports | SAP software | SYSPRO business software | Sage 300 Construction and Real Estate | Sage MAS 90 ERP | Sage Peachtree Premium Accounting for Manufacturing | Stratford Group INMASS/MRP | Structured query language SQL | Waterloo Hydrogeologic TACTIC | Work Technology WorkTech Time | Workbrain Employee Scheduling | Workbrain Time and Attendance | iCode Everest</t>
+  </si>
+  <si>
+    <t>Production and Processing | Customer and Personal Service | English Language | Administrative | Administration and Management | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Information Ordering | Oral Expression | Problem Sensitivity | Written Comprehension | Near Vision | Written Expression | Deductive Reasoning | Speech Recognition | Selective Attention | Category Flexibility | Speech Clarity | Perceptual Speed | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Time Pressure | E-Mail | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Contact With Others | Indoors, Environmentally Controlled | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Frequency of Decision Making | Spend Time Sitting | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Production and Operating Workers | Industrial Engineering Technologists and Technicians | Industrial Engineers | Industrial Production Managers | Laborers and Freight, Stock, and Material Movers, Hand | Logisticians | Logistics Analysts | Procurement Clerks | Project Management Specialists | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Supply Chain Managers | Team Assemblers | Transportation, Storage, and Distribution Managers | Weighers, Measurers, Checkers, and Samplers, Recordkeeping</t>
+  </si>
+  <si>
+    <t>Coordinate and expedite the flow of work and materials within or between departments of an establishment according to production schedule. Duties include reviewing and distributing production, work, and shipment schedules; conferring with department supervisors to determine progress of work and completion dates; and compiling reports on progress of work, inventory levels, costs, and production problems.</t>
+  </si>
+  <si>
+    <t>Arrange for delivery, assembly, or distribution of supplies or parts to expedite flow of materials and meet production schedules. | Calculate figures, such as required amounts of labor or materials, manufacturing costs, or wages, using pricing schedules, adding machines, calculators, or computers. | Compile and prepare documentation related to production sequences, transportation, personnel schedules, or purchase, maintenance, or repair orders. | Compile information, such as production rates and progress, materials inventories, materials used, or customer information, so that status reports can be completed. | Confer with department supervisors or other personnel to assess progress and discuss needed changes. | Confer with establishment personnel, vendors, or customers to coordinate production or shipping activities and to resolve complaints or eliminate delays. | Contact suppliers to verify shipment details. | Distribute production schedules or work orders to departments. | Establish and prepare product construction directions and locations and information on required tools, materials, equipment, numbers of workers needed, and cost projections. | Examine documents, materials, or products and monitor work processes to assess completeness, accuracy, and conformance to standards and specifications. | Maintain files, such as maintenance records, bills of lading, or cost reports. | Plan production commitments or timetables for business units, specific programs, or jobs, using sales forecasts. | Provide documentation and information to account for delays, difficulties, or changes to cost estimates. | Record production data, including volume produced, consumption of raw materials, or quality control measures. | Requisition and maintain inventories of materials or supplies necessary to meet production demands. | Review documents, such as production schedules, work orders, or staffing tables, to determine personnel or materials requirements or material priorities. | Revise production schedules when required due to design changes, labor or material shortages, backlogs, or other interruptions, collaborating with management, marketing, sales, production, or engineering.</t>
+  </si>
+  <si>
+    <t>43-5071.00</t>
+  </si>
+  <si>
+    <t>Shipping, Receiving, and Inventory Clerks</t>
+  </si>
+  <si>
+    <t>Materials Control Associate | Order Fulfillment Specialist | Receiver | Receiving Associate | Receiving Clerk | Receiving Coordinator | Shipper | Shipping Clerk | Shipping Coordinator | Traffic Assistant</t>
+  </si>
+  <si>
+    <t>ADi SmartBOL | AES MailSTAR | Accuship Star System | Aestiva Purchase Order | Apple Safari | Barcode labeling software | Bill of lading software | CMS Consultants WorldLink | Citrix cloud computing software | DM2 Bills of Lading | Dydacomp Mail Order Manager | Electronic Data Interchange EDI systems | Endicia Internet Postage | Enterprise Systems RFID Data Management | Exact MAX | FedEx Ship Manager | FileMaker Pro | Freight+ | Harvey Software CPS | IBM Notes | Infor ERP Visual | Inventory management systems | Inventory tracking software | Kewill Clippership | Kewill Compliance Partner | Kewill Javelin Distribution Ship | Laser Substrates PostalXport | MSR Visual Exporter | MSR Visual Exporter Document Library | MSR Visual Exporter Enterprise Integrator | Microsoft Dynamics GP | Microsoft Edge | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Mozilla Firefox | Oracle JD Edwards EnterpriseOne | Pitney Bowes ShipStream Manager | Precision TRA/X | SAP software | Sage 50 Accounting | ShipWorks | Shipping and freight management software | UPS Intelliverse | UPS WorldShip | Universal parcel shipping software | Varsity ShipSoft Supply Chain Execution Suite | Warehouse management system WMS | Web browser software | WindowBook Postal Package Partner</t>
+  </si>
+  <si>
+    <t>Speaking | Reading Comprehension | Active Listening | Monitoring | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Administrative | Computers and Electronics | Production and Processing | Mathematics | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Expression | Problem Sensitivity | Information Ordering | Oral Comprehension | Arm-Hand Steadiness | Speech Clarity | Speech Recognition | Manual Dexterity | Selective Attention | Perceptual Speed | Category Flexibility | Inductive Reasoning | Deductive Reasoning | Written Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Time Pressure | Indoors, Not Environmentally Controlled | Contact With Others | Telephone Conversations | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | Freedom to Make Decisions | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets</t>
+  </si>
+  <si>
+    <t>Cargo and Freight Agents | Couriers and Messengers | Dispatchers, Except Police, Fire, and Ambulance | Freight Forwarders | Laborers and Freight, Stock, and Material Movers, Hand | Logistics Analysts | Machine Feeders and Offbearers | Mail Clerks and Mail Machine Operators, Except Postal Service | Order Clerks | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Postal Service Clerks | Postal Service Mail Carriers | Postal Service Mail Sorters, Processors, and Processing Machine Operators | Procurement Clerks | Production, Planning, and Expediting Clerks | Stockers and Order Fillers | Tank Car, Truck, and Ship Loaders | Transportation, Storage, and Distribution Managers | Weighers, Measurers, Checkers, and Samplers, Recordkeeping</t>
+  </si>
+  <si>
+    <t>Verify and maintain records on incoming and outgoing shipments involving inventory. Duties include verifying and recording incoming merchandise or material and arranging for the transportation of products. May prepare items for shipment.</t>
+  </si>
+  <si>
+    <t>Compare shipping routes or methods to determine which have the least environmental impact. | Compute amounts, such as space available, shipping, storage, or demurrage charges, using computer or price list. | Confer or correspond with establishment representatives to rectify problems, such as damages, shortages, or nonconformance to specifications. | Contact carrier representatives to make arrangements or to issue instructions for shipping and delivery of materials. | Deliver or route materials to departments using handtruck, conveyor, or sorting bins. | Determine shipping methods, routes, or rates for materials to be shipped. | Examine shipment contents and compare with records, such as manifests, invoices, or orders, to verify accuracy. | Pack, seal, label, or affix postage to prepare materials for shipping, using hand tools, power tools, or postage meter. | Prepare documents, such as work orders, bills of lading, or shipping orders, to route materials. | Record shipment data, such as weight, charges, space availability, damages, or discrepancies, for reporting, accounting, or recordkeeping purposes. | Requisition and store shipping materials and supplies to maintain inventory of stock.</t>
+  </si>
+  <si>
+    <t>43-5111.00</t>
+  </si>
+  <si>
+    <t>Weighers, Measurers, Checkers, and Samplers, Recordkeeping</t>
+  </si>
+  <si>
+    <t>Cycle Counter | Fluid Operator | Inventory Specialist | Quality Assurance Inspector (QA Inspector) | Scale Operator | Supply Clerk | Temperature Taker</t>
+  </si>
+  <si>
+    <t>Email software | IBM Notes | Infor ERP Baan | Infor XA | Inventory management systems | Inventory software | Materials resource planning MRP software | Microsoft Access | Microsoft Dynamics AX | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | NetSuite ERP | Oracle Database | Oracle JD Edwards EnterpriseOne | Root cause analysis software | SAP software | Warehouse management system WMS</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Speaking | Monitoring | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mathematics | English Language | Administration and Management | Administrative</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Written Comprehension | Category Flexibility | Information Ordering | Perceptual Speed | Selective Attention | Oral Comprehension | Oral Expression | Deductive Reasoning | Written Expression | Speech Recognition | Flexibility of Closure | Speech Clarity | Far Vision | Finger Dexterity | Number Facility | Mathematical Reasoning | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Contact With Others | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing | Pace Determined by Speed of Equipment | Telephone Conversations | Indoors, Environmentally Controlled | Coordinate or Lead Others in Accomplishing Work Activities | Health and Safety of Other Workers | Freedom to Make Decisions | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Graders and Sorters, Agricultural Products | Inspectors, Testers, Sorters, Samplers, and Weighers | Laborers and Freight, Stock, and Material Movers, Hand | Laundry and Dry-Cleaning Workers | Log Graders and Scalers | Machine Feeders and Offbearers | Mixing and Blending Machine Setters, Operators, and Tenders | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Postal Service Mail Sorters, Processors, and Processing Machine Operators | Production, Planning, and Expediting Clerks | Recycling and Reclamation Workers | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Tank Car, Truck, and Ship Loaders | Textile Bleaching and Dyeing Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Weigh, measure, and check materials, supplies, and equipment for the purpose of keeping relevant records. Duties are primarily clerical by nature. Includes workers who collect and keep record of samples of products or materials.</t>
+  </si>
+  <si>
+    <t>Collect or prepare measurement, weight, or identification labels and attach them to products. | Collect product samples and prepare them for laboratory analysis or testing. | Communicate with customers and vendors to exchange information regarding products, materials, and services. | Compare product labels, tags, or tickets, shipping manifests, purchase orders, and bills of lading to verify accuracy of shipment contents, quality specifications, or weights. | Count or estimate quantities of materials, parts, or products received or shipped. | Document quantity, quality, type, weight, test result data, and value of materials or products to maintain shipping, receiving, and production records and files. | Examine products or materials, parts, subassemblies, and packaging for damage, defects, or shortages, using specification sheets, gauges, and standards charts. | Fill orders for products and samples, following order tickets, and forward or mail items. | Inspect products and examination records to determine the number of defects per worker and the reasons for examiners' rejections. | Maintain, monitor, and clean work areas, such as recycling collection sites, drop boxes, counters and windows, and areas around scale houses. | Operate scalehouse computers to obtain weight information about incoming shipments such as those from waste haulers. | Remove from stock products or loads not meeting quality standards, and notify supervisors or appropriate departments of discrepancies or shortages. | Signal or instruct other workers to weigh, move, or check products. | Sort products or materials into predetermined sequences or groupings for display, packing, shipping, or storage. | Store samples of finished products in labeled cartons and record their location. | Transport materials, products, or samples to processing, shipping, or storage areas, manually or using conveyors, pumps, or hand trucks. | Unload or unpack incoming shipments. | Weigh or measure materials, equipment, or products to maintain relevant records, using volume meters, scales, rules, or calipers.</t>
+  </si>
+  <si>
+    <t>43-6011.00</t>
+  </si>
+  <si>
+    <t>Executive Secretaries and Executive Administrative Assistants</t>
+  </si>
+  <si>
+    <t>Administrative Aide | Administrative Assistant | Administrative Associate | Administrative Coordinator | Administrative Secretary | Administrative Specialist | Executive Administrative Assistant | Executive Assistant | Executive Secretary | Office Assistant</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Adobe Contribute | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Aestiva Purchase Order | Airtable | Apple Keynote | Apple macOS | Appointment scheduling software | Blackbaud The Raiser's Edge | Cisco Webex | Corel WordPerfect Office Suite | Database software | Dropbox | Eko | Epicor Vantage ERP | Evernote | Exact Software Macola ES | Facebook | FileMaker Pro | Fishbowl Warehouse | Geac MPC Production | Google Docs | Google Drive | Google Meet | Google Sites | Google Slides | Google Workspace software | Graphics software | Human resource management software HRMS | IBM Notes | Inetsoft | Intrado SchoolMessenger | Intuit QuickBooks | JamBoard | KAPES | LexisNexis | LinkedIn | LogMeIn GoToMeeting | LogMeIn GoToWebinar | MTI Systems Costimator JS | Maynard PlanStaff Manager | Micro Estimating FabPlan | MicroStrategy Report Services | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Office software | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Team Foundation Server | Microsoft Visio | Microsoft Word | Oracle E-Business Suite Financials | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | PCC EHR | PCC Pediatric Partner | PRONTO Xi | ParentSquare | ProQuest RefWorks | ProQuest RefWorks RefShare | Questek Humanis | Records management systems | SAP Concur | SAP software | SYSPRO business software | Sage 50 Accounting | Sage Peachtree Premium Accounting for Manufacturing | Slack | Slido interaction software | SmugMug Flickr | Social media sites | Transcription software | Web browser software | Web conferencing software | Work Technology WorkTech Time | Workbrain Employee Scheduling | Workbrain Time and Attendance | Workflow International Deskflow Enterprise | Zoom</t>
+  </si>
+  <si>
+    <t>Active Listening | Reading Comprehension | Speaking | Writing | Critical Thinking | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>Administrative | English Language | Customer and Personal Service | Computers and Electronics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Speech Recognition | Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Near Vision | Speech Clarity | Information Ordering | Problem Sensitivity | Perceptual Speed | Category Flexibility | Deductive Reasoning | Selective Attention | Flexibility of Closure | Inductive Reasoning | Originality | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | E-Mail | Contact With Others | Determine Tasks, Priorities and Goals | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Spend Time Sitting | Indoors, Environmentally Controlled | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Written Letters and Memos | Deal With External Customers or the Public in General | Time Pressure | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Chief Executives | Correspondence Clerks | Eligibility Interviewers, Government Programs | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | Human Resources Assistants, Except Payroll and Timekeeping | Human Resources Specialists | Legal Secretaries and Administrative Assistants | Management Analysts | Medical Secretaries and Administrative Assistants | Office Clerks, General | Paralegals and Legal Assistants | Project Management Specialists | Public Relations Managers | Public Relations Specialists | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Social Science Research Assistants</t>
+  </si>
+  <si>
+    <t>Provide high-level administrative support by conducting research, preparing statistical reports, and handling information requests, as well as performing routine administrative functions such as preparing correspondence, receiving visitors, arranging conference calls, and scheduling meetings. May also train and supervise lower-level clerical staff.</t>
+  </si>
+  <si>
+    <t>Answer phone calls and direct calls to appropriate parties or take messages. | Attend meetings to record minutes. | Compile, transcribe, and distribute minutes of meetings. | Conduct research, compile data, and prepare papers for consideration and presentation by executives, committees, and boards of directors. | Coordinate and direct office services, such as records, departmental finances, budget preparation, personnel issues, and housekeeping, to aid executives. | File and retrieve corporate documents, records, and reports. | Greet visitors and determine whether they should be given access to specific individuals. | Interpret administrative and operating policies and procedures for employees. | Make travel arrangements for executives. | Manage and maintain executives' schedules. | Meet with individuals, special interest groups, and others on behalf of executives, committees, and boards of directors. | Open, sort, and distribute incoming correspondence, including faxes and email. | Perform general office duties, such as ordering supplies, maintaining records management database systems, and performing basic bookkeeping work. | Prepare agendas and make arrangements, such as coordinating catering for luncheons, for committee, board, and other meetings. | Prepare invoices, reports, memos, letters, financial statements, and other documents, using word processing, spreadsheet, database, or presentation software. | Prepare responses to correspondence containing routine inquiries. | Process payroll information. | Provide clerical support to other departments. | Read and analyze incoming memos, submissions, and reports to determine their significance and plan their distribution. | Review operating practices and procedures to determine whether improvements can be made in areas such as workflow, reporting procedures, or expenditures. | Set up and oversee administrative policies and procedures for offices or organizations. | Supervise and train other clerical staff and arrange for employee training by scheduling training or organizing training material.</t>
+  </si>
+  <si>
+    <t>43-6012.00</t>
+  </si>
+  <si>
+    <t>Legal Secretaries and Administrative Assistants</t>
+  </si>
+  <si>
+    <t>Confidential Secretary | Legal Administrative Assistant (Legal Admin Assistant) | Legal Administrator (Legal Admin) | Legal Coordinator | Legal Management Assistant | Legal Office Support Assistant | Legal Practice Assistant | Legal Secretary | Litigation Secretary | Magistrate Assistant</t>
+  </si>
+  <si>
+    <t>A1-Law | ADP Workforce Now | AbacusNext HotDocs | Aderant CompuLaw | Adobe Acrobat | Amortization calculation software | Appointment scheduling software | Billing software | Case management software | Chrome River Expense | Database software | Dropbox | Electronic adjudication management systems EAM | Electronic diary software | Email software | Filing system software | IBM Lotus Notes | Intuit QuickBooks | Legal research software | Legal software | LexisNexis | LexisNexis Time Matters | Litigation management software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Word | Public access to electronic court records PACER | Quicken | Sage 50 Accounting | Thomson Reuters Elite Billing Manager | Thomson Reuters Westlaw | Transcription software | Vertican Technologies Collection Master | Web browser software | Web conferencing software | Web page design and editing software | WordPerfect</t>
+  </si>
+  <si>
+    <t>Active Listening | Reading Comprehension | Writing | Speaking | Monitoring | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Administrative | English Language | Law and Government | Customer and Personal Service | Computers and Electronics | Administration and Management | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Near Vision | Oral Expression | Written Expression | Speech Clarity | Speech Recognition | Information Ordering | Selective Attention | Category Flexibility | Deductive Reasoning | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>E-Mail | Importance of Being Exact or Accurate | Contact With Others | Telephone Conversations | Importance of Repeating Same Tasks | Spend Time Sitting | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Written Letters and Memos | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Deal With External Customers or the Public in General</t>
+  </si>
+  <si>
+    <t>Administrative Law Judges, Adjudicators, and Hearing Officers | Administrative Services Managers | Compliance Officers | Correspondence Clerks | Court Reporters and Simultaneous Captioners | Court, Municipal, and License Clerks | Eligibility Interviewers, Government Programs | Executive Secretaries and Executive Administrative Assistants | File Clerks | Human Resources Assistants, Except Payroll and Timekeeping | Insurance Claims and Policy Processing Clerks | Judicial Law Clerks | Lawyers | Medical Records Specialists | Medical Secretaries and Administrative Assistants | Office Clerks, General | Paralegals and Legal Assistants | Private Detectives and Investigators | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive</t>
+  </si>
+  <si>
+    <t>Perform secretarial duties using legal terminology, procedures, and documents. Prepare legal papers and correspondence, such as summonses, complaints, motions, and subpoenas. May also assist with legal research.</t>
+  </si>
+  <si>
+    <t>Assist attorneys in collecting information such as employment, medical, and other records. | Attend legal meetings, such as client interviews, hearings, or depositions, and take notes. | Complete various forms, such as accident reports, trial and courtroom requests, and applications for clients. | Draft and type office memos. | Mail, fax, or arrange for delivery of legal correspondence to clients, witnesses, and court officials. | Make photocopies of correspondence, documents, and other printed matter. | Make travel arrangements for attorneys. | Organize and maintain law libraries, documents, and case files. | Prepare and distribute invoices to bill clients or pay account expenses. | Prepare, proofread, or process legal documents, such as summonses, subpoenas, complaints, appeals, motions, or pretrial agreements. | Receive and place telephone calls. | Review legal publications and perform database searches to identify laws and court decisions relevant to pending cases. | Schedule and make appointments. | Submit articles and information from searches to attorneys for review and approval for use.</t>
+  </si>
+  <si>
+    <t>43-6013.00</t>
+  </si>
+  <si>
+    <t>Medical Secretaries and Administrative Assistants</t>
+  </si>
+  <si>
+    <t>Clinic Office Assistant | Front Desk Receptionist | Medical Office Specialist | Medical Receptionist | Medical Secretary | Physician Office Specialist | Secretary | Unit Clerk | Unit Support Representative | Ward Clerk</t>
+  </si>
+  <si>
+    <t>Accounts payable software | Accounts receivable software | Addressing software | Allscripts Payerpath | Allscripts Professional PM | Amazing Charts | Billing software | CPSI CPSI System | Corel WordPerfect Office Suite | Data entry software | Database software | Electronic health record EHR software | Email software | Epic Systems | Google Docs | Google Drive | Graphics software | HMS | Healthcare common procedure coding system HCPCS | Henry Schein Dentrix | IDX Groupcast | Intuit QuickBooks | Intuit QuickBooks Point of Sale | MEDENT | MEDITECH Medical and Practice Management MPM Suite | MEDITECH software | McKesson Lytec | Medical condition coding software | Medical procedure coding software | Microsoft Access | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Windows | Microsoft Word | Microsys MicroMD | NaviMedix NaviNet | Patterson Dental Supply Patterson EagleSoft | PracticeWorks Systems Kodak WINOMS CS | Scheduling software | Web browser software | Wisconsin Physicians Service Insurance CMS Secure Net Access Portal C-SNAP | dBASE Plus | eClinicalWorks EHR software | eMDs Medisoft</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Writing | Critical Thinking | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administrative | Medicine and Dentistry | Personnel and Human Resources | Computers and Electronics | Administration and Management | Economics and Accounting</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Speech Recognition | Speech Clarity | Near Vision | Information Ordering | Inductive Reasoning | Deductive Reasoning | Written Expression | Category Flexibility | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Contact With Others | Importance of Repeating Same Tasks | Spend Time Sitting | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Written Letters and Memos | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Coordinate or Lead Others in Accomplishing Work Activities | Freedom to Make Decisions | Deal With External Customers or the Public in General | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Billing and Posting Clerks | Customer Service Representatives | Eligibility Interviewers, Government Programs | Emergency Medicine Physicians | Executive Secretaries and Executive Administrative Assistants | First-Line Supervisors of Office and Administrative Support Workers | Health Information Technologists and Medical Registrars | Human Resources Assistants, Except Payroll and Timekeeping | Insurance Claims and Policy Processing Clerks | Interviewers, Except Eligibility and Loan | Medical Assistants | Medical Records Specialists | Medical Transcriptionists | Medical and Health Services Managers | Office Clerks, General | Patient Representatives | Pharmacy Technicians | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive</t>
+  </si>
+  <si>
+    <t>Perform secretarial duties using specific knowledge of medical terminology and hospital, clinic, or laboratory procedures. Duties may include scheduling appointments, billing patients, and compiling and recording medical charts, reports, and correspondence.</t>
+  </si>
+  <si>
+    <t>Answer telephones and direct calls to appropriate staff. | Compile and record medical charts, reports, or correspondence, using typewriter or personal computer. | Complete insurance or other claim forms. | Greet visitors, ascertain purpose of visit, and direct them to appropriate staff. | Interview patients to complete documents, case histories, or forms, such as intake or insurance forms. | Maintain medical records, technical library, or correspondence files. | Operate office equipment, such as voice mail messaging systems, and use word processing, spreadsheet, or other software applications to prepare reports, invoices, financial statements, letters, case histories, or medical records. | Perform bookkeeping duties, such as credits or collections, preparing and sending financial statements or bills, and keeping financial records. | Perform various clerical or administrative functions, such as ordering and maintaining an inventory of supplies. | Prepare correspondence or assist physicians or medical scientists with preparation of reports, speeches, articles, or conference proceedings. | Receive and route messages or documents, such as laboratory results, to appropriate staff. | Schedule and confirm patient diagnostic appointments, surgeries, or medical consultations. | Schedule tests or procedures for patients, such as lab work or x-rays, based on physician orders. | Transcribe recorded messages or practitioners' diagnoses or recommendations into patients' medical records. | Transmit correspondence or medical records by mail, e-mail, or fax.</t>
+  </si>
+  <si>
+    <t>43-6014.00</t>
+  </si>
+  <si>
+    <t>Secretaries and Administrative Assistants, Except Legal, Medical, and Executive</t>
+  </si>
+  <si>
+    <t>Administrative Assistant (Admin Assistant) | Administrative Clerk | Administrative Secretary (Admin Secretary) | Administrative Specialist (Admin Specialist) | Administrative Support Assistant (ASA) | Administrative Technician | Department Secretary | Office Assistant | Secretary | Staff Assistant</t>
+  </si>
+  <si>
+    <t>3M Post-it App | ADP Workforce Now | Adobe Acrobat | Adobe Creative Cloud software | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Airtable | Apache Cassandra | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Pig | Apache Solr | Apache Tomcat | Apple Keynote | Apple macOS | Appointment scheduling software | Atlassian Confluence | Atlassian JIRA | Blackbaud The Raiser's Edge | Blackboard software | Canva | Cisco Webex | Citrix cloud computing software | ClassDojo | Customer information control system CICS | Data entry software | Data warehouse software | Database software | Delphi Technology | Dictation software | Dropbox | Drupal | Evernote | FaceTime | Facebook | FileMaker Pro | Filing system software | Fund accounting software | Google Docs | Google Drive | Google Meet | Google Sheets | Google Sites | Google Slides | Google Workspace software | GroupMe | Handheld computer device software | Human resource management software HRMS | Hypertext markup language HTML | IBM Cognos Impromptu | IBM InfoSphere DataStage | IBM Maximo Asset Management | IBM Notes | IBM Power Systems software | IBM SPSS Statistics | IBM WebSphere | Intrado SchoolMessenger | Intuit QuickBooks | Kronos Workforce Timekeeper | LexisNexis | LinkedIn | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Loom | McAfee | Medical procedure coding software | MicroStrategy | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Dynamics SL | Microsoft Excel | Microsoft Exchange | Microsoft Office software | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Windows | Microsoft Word | Minitab | Mozilla Firefox | NetSuite ERP | NortonLifeLock cybersecurity software | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Qlik Tech QlikView | Quest Erwin Data Modeler | SAP Business Objects | SAP Concur | SAP Crystal Reports | SAP software | SAS | Sage 50 Accounting | Salesforce software | Schoology | Skype | Slack | SmugMug Flickr | Social media sites | Tax software | Teradata Database | Timekeeping software | Veritas NetBackup | Web browser software | Web conferencing software | Yardi software | YouTube | Zoom | people@work</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension | Writing | Monitoring | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Administrative | English Language | Computers and Electronics | Customer and Personal Service | Administration and Management</t>
+  </si>
+  <si>
+    <t>Written Expression | Oral Comprehension | Written Comprehension | Oral Expression | Near Vision | Speech Recognition | Speech Clarity | Information Ordering | Problem Sensitivity | Selective Attention | Category Flexibility | Inductive Reasoning | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Spend Time Sitting | Importance of Repeating Same Tasks | Determine Tasks, Priorities and Goals | Written Letters and Memos | Importance of Being Exact or Accurate | Time Pressure | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Chief Executives | Correspondence Clerks | Court, Municipal, and License Clerks | Customer Service Representatives | Eligibility Interviewers, Government Programs | Executive Secretaries and Executive Administrative Assistants | File Clerks | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | Human Resources Assistants, Except Payroll and Timekeeping | Human Resources Specialists | Interviewers, Except Eligibility and Loan | Legal Secretaries and Administrative Assistants | Management Analysts | Medical Secretaries and Administrative Assistants | Office Clerks, General | Receptionists and Information Clerks | Social Science Research Assistants | Switchboard Operators, Including Answering Service</t>
+  </si>
+  <si>
+    <t>Perform routine administrative functions such as drafting correspondence, scheduling appointments, organizing and maintaining paper and electronic files, or providing information to callers.</t>
+  </si>
+  <si>
+    <t>Answer telephones and give information to callers, take messages, or transfer calls to appropriate individuals. | Arrange conference, meeting, or travel reservations for office personnel. | Collect and deposit money into accounts, disburse funds from cash accounts to pay bills or invoices, keep records of collections and disbursements, and ensure accounts are balanced. | Complete forms in accordance with company procedures. | Compose, type, and distribute meeting notes, routine correspondence, or reports, such as presentations or expense, statistical, or monthly reports. | Conduct searches to find needed information, using such sources as the Internet. | Coordinate conferences, meetings, or special events, such as luncheons or graduation ceremonies. | Create, maintain, and enter information into databases. | Develop or maintain internal or external company Web sites. | Establish work procedures or schedules and keep track of the daily work of clerical staff. | Greet visitors or callers and handle their inquiries or direct them to the appropriate persons according to their needs. | Learn to operate new office technologies as they are developed and implemented. | Locate and attach appropriate files to incoming correspondence requiring replies. | Mail newsletters, promotional material, or other information. | Maintain scheduling and event calendars. | Make copies of correspondence or other printed material. | Manage projects or contribute to committee or team work. | Open, read, route, and distribute incoming mail or other materials and answer routine letters. | Operate electronic mail systems and coordinate the flow of information, internally or with other organizations. | Operate office equipment, such as fax machines, copiers, or phone systems and arrange for repairs when equipment malfunctions. | Order and dispense supplies. | Perform payroll functions, such as maintaining timekeeping information and processing and submitting payroll. | Prepare and mail checks. | Prepare conference or event materials, such as flyers or invitations. | Provide services to customers, such as order placement or account information. | Review work done by others to check for correct spelling and grammar, ensure that company format policies are followed, and recommend revisions. | Schedule and confirm appointments for clients, customers, or supervisors. | Set up and manage paper or electronic filing systems, recording information, updating paperwork, or maintaining documents, such as attendance records, correspondence, or other material. | Supervise other clerical staff and provide training and orientation to new staff. | Train and assist staff with computer usage. | Use computers for various applications, such as database management or word processing.</t>
+  </si>
+  <si>
+    <t>43-9021.00</t>
+  </si>
+  <si>
+    <t>Data Entry Keyers</t>
+  </si>
+  <si>
+    <t>Data Capture Specialist | Data Entry Clerk | Data Entry Machine Operator | Data Entry Operator | Data Entry Specialist | Data Transcriber | Records Clerk | Underwriting Support Specialist</t>
+  </si>
+  <si>
+    <t>Blackbaud The Raiser's Edge | Data entry software | Database software | Electronic medical record EMR software | FaceTime | FileMaker Pro | Google Docs | Google Drive | Healthcare common procedure coding system HCPCS | IBM Informix | Intuit QuickBooks | Jenzabar ERP | Medical condition coding software | Medical procedure coding software | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Perceptive Software Intelligent Capture | SAP software | Sage 50 Accounting | Salesforce.com Salesforce CRM</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>English Language | Administrative | Customer and Personal Service | Law and Government</t>
+  </si>
+  <si>
+    <t>Written Comprehension | Near Vision | Finger Dexterity | Information Ordering | Oral Comprehension | Speech Recognition | Perceptual Speed | Selective Attention | Speech Clarity | Wrist-Finger Speed | Category Flexibility | Written Expression | Inductive Reasoning | Oral Expression</t>
+  </si>
+  <si>
+    <t>Spend Time Sitting | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Spend Time Making Repetitive Motions | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Determine Tasks, Priorities and Goals | Contact With Others | Time Pressure | Telephone Conversations | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Calibration Technologists and Technicians | Correspondence Clerks | Document Management Specialists | File Clerks | Mail Clerks and Mail Machine Operators, Except Postal Service | Medical Records Specialists | Office Clerks, General | Office Machine Operators, Except Computer | Payroll and Timekeeping Clerks | Postal Service Mail Sorters, Processors, and Processing Machine Operators | Production, Planning, and Expediting Clerks | Proofreaders and Copy Markers | Shipping, Receiving, and Inventory Clerks | Statistical Assistants | Switchboard Operators, Including Answering Service | Title Examiners, Abstractors, and Searchers | Weighers, Measurers, Checkers, and Samplers, Recordkeeping | Word Processors and Typists</t>
+  </si>
+  <si>
+    <t>Operate data entry device, such as keyboard or photo composing perforator. Duties may include verifying data and preparing materials for printing.</t>
+  </si>
+  <si>
+    <t>Compare data with source documents, or re-enter data in verification format to detect errors. | Compile, sort, and verify the accuracy of data before it is entered. | Load machines with required input or output media, such as paper, cards, disks, tape, or Braille media. | Locate and correct data entry errors, or report them to supervisors. | Maintain logs of activities and completed work. | Read source documents such as canceled checks, sales reports, or bills, and enter data in specific data fields or onto tapes or disks for subsequent entry, using keyboards or scanners. | Resolve garbled or indecipherable messages, using cryptographic procedures and equipment. | Select materials needed to complete work assignments. | Store completed documents in appropriate locations.</t>
+  </si>
+  <si>
+    <t>43-9022.00</t>
+  </si>
+  <si>
+    <t>Word Processors and Typists</t>
+  </si>
+  <si>
+    <t>Clerk Specialist | Clerk Typist | Keyboard Specialist | Office Technician | Stenographer | Typist | Word Processor</t>
+  </si>
+  <si>
+    <t>Act! | Adobe Acrobat | Blackbaud CRM | Corel WordPerfect Office Suite | FileMaker Pro | Google Workspace software | IBM Notes | Intuit QuickBooks | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Oracle PeopleSoft | Oracle Siebel CRM | SAP software | SRSsoft SRS EHR</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Writing | Active Listening | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Administrative | English Language | Customer and Personal Service | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Near Vision | Written Comprehension | Speech Recognition | Oral Comprehension | Written Expression | Wrist-Finger Speed | Information Ordering | Oral Expression | Speech Clarity | Finger Dexterity | Perceptual Speed | Category Flexibility | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Spend Time Sitting | E-Mail | Contact With Others | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Deal With External Customers or the Public in General | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Time Pressure | Coordinate or Lead Others in Accomplishing Work Activities | Written Letters and Memos | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Correspondence Clerks | Court Reporters and Simultaneous Captioners | Data Entry Keyers | Document Management Specialists | Executive Secretaries and Executive Administrative Assistants | File Clerks | Legal Secretaries and Administrative Assistants | Medical Records Specialists | Medical Secretaries and Administrative Assistants | Medical Transcriptionists | Office Clerks, General | Office Machine Operators, Except Computer | Proofreaders and Copy Markers | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Statistical Assistants | Switchboard Operators, Including Answering Service | Title Examiners, Abstractors, and Searchers</t>
+  </si>
+  <si>
+    <t>Use word processor, computer, or typewriter to type letters, reports, forms, or other material from rough draft, corrected copy, or voice recording. May perform other clerical duties as assigned.</t>
+  </si>
+  <si>
+    <t>Address envelopes or prepare envelope labels, using typewriter or computer. | Adjust settings for format, page layout, line spacing, and other style requirements. | Check completed work for spelling, grammar, punctuation, and format. | Collate pages of reports and other documents. | Compute and verify totals on report forms, requisitions, or bills, using adding machine or calculator. | Electronically sort and compile text and numerical data, retrieving, updating, and merging documents as required. | File and store completed documents on computer hard drive or disk, or maintain a computer filing system to store, retrieve, update, and delete documents. | Gather, register, and arrange the material to be typed, following instructions. | Keep records of work performed. | Manage schedules and set dates, times, and locations for meetings and appointments. | Operate and resupply printers and computers, changing print wheels or fluid cartridges, adding paper, and loading blank tapes, cards, or disks into equipment. | Perform other clerical duties, such as answering telephone, sorting and distributing mail, running errands or sending faxes. | Print and make copies of work. | Reformat documents, moving paragraphs or columns. | Search for specific sets of stored, typed characters to make changes. | Transmit work electronically to other locations. | Type correspondence, reports, text and other written material from rough drafts, corrected copies, voice recordings, dictation, or previous versions, using a computer, word processor, or typewriter. | Use data entry devices, such as optical scanners, to input data into computers for revision or editing. | Work with technical material, preparing statistical reports, planning and typing statistical tables, and combining and rearranging material from different sources.</t>
+  </si>
+  <si>
+    <t>43-9031.00</t>
+  </si>
+  <si>
+    <t>Desktop Publishers</t>
+  </si>
+  <si>
+    <t>Advertising Associate | Compositor | Computer Typesetter | Design Editor | Desktop Operator | Desktop Publishing Specialist | Electronic Console Display Operator | Electronic Imager | Electronic Publishing Specialist | Publisher</t>
+  </si>
+  <si>
+    <t>AT&amp;T Troff | Actuate DocBook | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | Adobe Creative Cloud software | Adobe Dreamweaver | Adobe FrameMaker | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe LiveMotion | Adobe PageMaker | Adobe Photoshop | Adobe PostScript | AlgoLab Raster to Vector Conversion Toolkit | Apple AppleScript | Apple iPhoto | Apple macOS | Arts &amp; Letters Express | Cascading style sheets CSS | Cenon | CodedColor | Color management software | Corel CorelDraw Graphics Suite | Corel CorelScan | Corel OCR-Trace 8 | Corel Paint Shop Pro | Corel Photo-Paint | Corel Ventura | Corel WebDraw | Corel WordPerfect Office Suite | EMC Documentum | Extensible markup language XML | Finite Matters PatternStream | GNU Image Manipulation Program GIMP | GTX RastorCAD | Graphics software | GrassHopper PageStream | Hypertext markup language HTML | Inkscape | JavaScript | LaTeX | Mapping software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Picture It! | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | MySQL | Nuance Dragon NaturallySpeaking | Nuance OmniPage Professional | Objectif Lune PlanetPress Suite | Online image and graphics database software | OpenOffice.org | Oracle Java | PANTONE ColorVision ProfilerPlus | PHP | Perl | Portable document file creation software | Potrace | Python | QuarkXPress | Raster graphics editors | SAP software | Salesforce software | Scalable vector graphics SVG | Scribus | Serif PagePlus | Social media software | Spelling and grammar checking software | Sun Microsystems Java | Trix TracTrix | UNIX | Ulead PhotoImpact | Vector drawing software | Virtual private networking VPN software | WordWeb | Xara Designer Pro | jQuery</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Communications and Media | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Information Ordering | Originality | Visualization | Written Comprehension | Fluency of Ideas | Oral Comprehension | Written Expression | Problem Sensitivity | Category Flexibility | Visual Color Discrimination | Perceptual Speed | Deductive Reasoning | Oral Expression | Selective Attention | Speech Clarity | Speech Recognition | Far Vision | Inductive Reasoning | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>E-Mail | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Sitting | Time Pressure | Importance of Being Exact or Accurate | Contact With Others | Telephone Conversations | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Art Directors | Computer Programmers | Computer Systems Analysts | Data Entry Keyers | Document Management Specialists | Editors | File Clerks | Film and Video Editors | Graphic Designers | Office Machine Operators, Except Computer | Photographic Process Workers and Processing Machine Operators | Prepress Technicians and Workers | Proofreaders and Copy Markers | Software Developers | Special Effects Artists and Animators | Technical Writers | Video Game Designers | Web Administrators | Web Developers | Web and Digital Interface Designers</t>
+  </si>
+  <si>
+    <t>Format typescript and graphic elements using computer software to produce publication-ready material.</t>
+  </si>
+  <si>
+    <t>Check preliminary and final proofs for errors and make necessary corrections. | Collaborate with graphic artists, editors and writers to produce master copies according to design specifications. | Convert various types of files for printing or for the Internet, using computer software. | Create special effects such as vignettes, mosaics, and image combining, and add elements such as sound and animation to electronic publications. | Edit graphics and photos, using pixel or bitmap editing, airbrushing, masking, or image retouching. | Enter data, such as coordinates of images and color specifications, into system to retouch and make color corrections. | Enter digitized data into electronic prepress system computer memory, using scanner, camera, keyboard, or mouse. | Enter text into computer keyboard and select the size and style of type, column width, and appropriate spacing for printed materials. | Import text and art elements, such as electronic clip art or electronic files from photographs that have been scanned or produced with a digital camera, using computer software. | Load floppy disks or tapes containing information into system. | Operate desktop publishing software and equipment to design, lay out, and produce camera-ready copy. | Position text and art elements from a variety of databases in a visually appealing way to design print or web pages, using knowledge of type styles and size and layout patterns. | Prepare sample layouts for approval, using computer software. | Select number of colors and determine color separations. | Store copies of publications on paper, magnetic tape, film, or diskette. | Study layout or other design instructions to determine work to be done and sequence of operations. | Transmit, deliver, or mail publication master to printer for production into film and plates. | View monitors for visual representation of work in progress and for instructions and feedback throughout process, making modifications as necessary.</t>
+  </si>
+  <si>
+    <t>43-9041.00</t>
+  </si>
+  <si>
+    <t>Insurance Claims and Policy Processing Clerks</t>
+  </si>
+  <si>
+    <t>Claims Adjudicator | Claims Analyst | Claims Clerk | Claims Customer Service Representative (Claims CSR) | Claims Processor | Claims Representative (Claims Rep) | Claims Technician (Claims Tech) | Insurance Analyst | Policy Analyst | Underwriting Assistant</t>
+  </si>
+  <si>
+    <t>Account management software | Alpha Software Alpha Five | Automated information system software | Billing software | Claim processing system software | Database software | GroupMe | Healthcare common procedure coding system HCPCS | IBM Check Processing Control System CPSC | IBM Lotus Notes | InSystems Calligo Enterprise | Insurance rating software | Medical condition coding software | Medical procedure coding software | MicroFocus GroupWise | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Policy issuance system software | St. Paul Travelers e-CARMA | Web browser software | Xactware Xactimate</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Speech Clarity | Speech Recognition | Oral Expression | Near Vision | Written Expression | Information Ordering | Deductive Reasoning | Problem Sensitivity | Category Flexibility | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>E-Mail | Spend Time Sitting | Telephone Conversations | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Indoors, Environmentally Controlled | Contact With Others | Determine Tasks, Priorities and Goals | Written Letters and Memos | Work With or Contribute to a Work Group or Team | Time Pressure | Spend Time Making Repetitive Motions | Face-to-Face Discussions with Individuals and Within Teams | Frequency of Decision Making | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General</t>
+  </si>
+  <si>
+    <t>Bill and Account Collectors | Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Brokerage Clerks | Claims Adjusters, Examiners, and Investigators | Compensation, Benefits, and Job Analysis Specialists | Correspondence Clerks | Credit Authorizers, Checkers, and Clerks | Customer Service Representatives | Eligibility Interviewers, Government Programs | Insurance Sales Agents | Insurance Underwriters | Legal Secretaries and Administrative Assistants | Loan Interviewers and Clerks | Medical Records Specialists | New Accounts Clerks | Office Clerks, General | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Tax Examiners and Collectors, and Revenue Agents | Title Examiners, Abstractors, and Searchers</t>
+  </si>
+  <si>
+    <t>Process new insurance policies, modifications to existing policies, and claims forms. Obtain information from policyholders to verify the accuracy and completeness of information on claims forms, applications and related documents, and company records. Update existing policies and company records to reflect changes requested by policyholders and insurance company representatives.</t>
+  </si>
+  <si>
+    <t>Calculate amount of claim. | Calculate premiums, refunds, commissions, adjustments, or new reserve requirements, using insurance rate standards. | Collect initial premiums and issue receipts. | Compare information from application to criteria for policy reinstatement, and approve reinstatement when criteria are met. | Compose business correspondence for supervisors, managers, and professionals. | Contact insured or other involved persons to obtain missing information. | Correspond with insured or agent to obtain information or to inform them of account status or changes. | Enter insurance- and claims-related information into database systems. | Examine letters from policyholders or agents, original insurance applications, and other company documents to determine if changes are needed and effects of changes. | Interview clients and take their calls to provide customer service and obtain information on claims. | Modify, update, or process existing policies and claims to reflect any change in beneficiary, amount of coverage, or type of insurance. | Notify insurance agent and accounting department of policy cancellation. | Obtain computer printout of policy cancellations, or retrieve cancellation cards from file. | Organize or work with detailed office or warehouse records, maintaining files for each policyholder, including policies that are to be reinstated or cancelled. | Organize or work with detailed office or warehouse records, using computers to enter, access, search or retrieve data. | Pay small claims. | Post or attach information to claim file. | Prepare insurance claim forms or related documents, and review them for completeness. | Process and record new insurance policies and claims. | Process, prepare, and submit business or government forms, such as submitting applications for coverage to insurance carriers. | Provide customer service, such as limited instructions on proceeding with claims or referrals to auto repair facilities or local contractors. | Review and verify data, such as age, name, address, and principal sum and value of property, on insurance applications and policies. | Review insurance policy to determine coverage. | Transcribe data to worksheets, and enter data into computer for use in preparing documents and adjusting accounts. | Transmit claims for payment or further investigation.</t>
+  </si>
+  <si>
+    <t>43-9051.00</t>
+  </si>
+  <si>
+    <t>Mail Clerks and Mail Machine Operators, Except Postal Service</t>
+  </si>
+  <si>
+    <t>Insert Operator | Inserter Operator | Mail Clerk | Mail Handler | Mail Machine Operator | Mail Processor | Mail Reader | Mail Sorter | Postal Clerk</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Email software | Financial accounting software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Postal Explorer | Recordkeeping software | Web browser software</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Comprehension | Written Comprehension | Speech Recognition | Finger Dexterity | Manual Dexterity | Category Flexibility | Information Ordering | Arm-Hand Steadiness | Deductive Reasoning | Problem Sensitivity | Oral Expression</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Telephone Conversations | E-Mail | Frequency of Decision Making | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Repeating Same Tasks | Time Pressure | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Spend Time Making Repetitive Motions | Physical Proximity | Spend Time Standing | Work Outcomes and Results of Other Workers | Written Letters and Memos | Deal With External Customers or the Public in General</t>
+  </si>
+  <si>
+    <t>Cargo and Freight Agents | Cashiers | Couriers and Messengers | Data Entry Keyers | File Clerks | Laborers and Freight, Stock, and Material Movers, Hand | Light Truck Drivers | Office Clerks, General | Office Machine Operators, Except Computer | Order Clerks | Packers and Packagers, Hand | Postal Service Clerks | Postal Service Mail Carriers | Postal Service Mail Sorters, Processors, and Processing Machine Operators | Postmasters and Mail Superintendents | Receptionists and Information Clerks | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Switchboard Operators, Including Answering Service | Weighers, Measurers, Checkers, and Samplers, Recordkeeping</t>
+  </si>
+  <si>
+    <t>Prepare incoming and outgoing mail for distribution. Time-stamp, open, read, sort, and route incoming mail; and address, seal, stamp, fold, stuff, and affix postage to outgoing mail or packages. Duties may also include keeping necessary records and completed forms.</t>
+  </si>
+  <si>
+    <t>Accept and check containers of mail or parcels from large volume mailers, couriers, and contractors. | Add ink, fill paste reservoirs, and change machine ribbons when necessary. | Adjust guides, rollers, loose card inserters, weighing machines, and tying arms, using rules and hand tools. | Affix postage to packages or letters by hand, or stamp materials, using postage meters. | Answer inquiries regarding shipping or mailing policies. | Clear jams in sortation equipment. | Contact delivery or courier services to arrange delivery of letters and parcels. | Determine manner in which mail is to be sent, and prepare it for delivery to mailing facilities. | Fold letters or circulars and insert them in envelopes. | Inspect mail machine output for defects and determine how to eliminate causes of any defects. | Lift and unload containers of mail or parcels onto equipment for transportation to sortation stations. | Mail merchandise samples or promotional literature in response to requests. | Operate computer-controlled keyboards or voice recognition equipment to direct items according to established routing schemes. | Place incoming or outgoing letters or packages into sacks or bins based on destination or type, and place identifying tags on sacks or bins. | Read production orders to determine types and sizes of items scheduled for printing and mailing. | Release packages or letters to customers upon presentation of written notices or other identification. | Remove containers of sorted mail or parcels and transfer them to designated areas according to established procedures. | Remove from machines printed materials, such as labeled articles, postmarked envelopes or tape, and folded sheets. | Seal or open envelopes, by hand or by using machines. | Sell mail products, and accept payment for products and mailing charges. | Sort and route incoming mail, and collect outgoing mail, using carts as necessary. | Stamp dates and times of receipt of incoming mail. | Start machines that automatically feed plates, stencils, or tapes through mechanisms, and observe machine operations to detect any malfunctions. | Verify that items are addressed correctly, marked with the proper postage, and in suitable condition for processing. | Weigh packages or letters to determine postage needed, using weighing scales and rate charts. | Wrap packages or bundles by hand, or by using tying machines.</t>
+  </si>
+  <si>
+    <t>43-9061.00</t>
+  </si>
+  <si>
+    <t>Office Clerks, General</t>
+  </si>
+  <si>
+    <t>Administrative Clerk (Admin Clerk) | Clerical Aide | Clerical Assistant | Clerk | General Clerk | Office Assistant | Office Clerk | Office Services Specialist | Office Support Assistant</t>
+  </si>
+  <si>
+    <t>3M Post-it App | ADP Workforce Now | Adobe Acrobat | Adobe InDesign | Alpha Software Alpha Five | Appointment scheduling software | Billing software | Blackbaud The Raiser's Edge | Blackboard software | Bookkeeping software | Data entry software | Database software | Dropbox | Electronic Data Interchange EDI systems | Evernote | Facebook | FileMaker Pro | Filing system software | Google Docs | Google Drive | Google Sites | Google Workspace software | GroupMe | Henry Schein Dentrix | IBM Check Processing Control System CPSC | IBM Notes | Intuit QuickBooks | LexisNexis | LinkedIn | MEDITECH software | Mavenlink | Medical condition coding software | Medical procedure coding software | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Propertyware | Records management software | SAP software | Sage 50 Accounting | Salesforce.com Salesforce CRM | SmugMug Flickr | Social media sites | St. Paul Travelers e-CARMA | Transcription system software | Web browser software | Yardi software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Speaking | Writing | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Administrative | English Language | Customer and Personal Service | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Written Comprehension | Written Expression | Speech Recognition | Speech Clarity | Near Vision | Problem Sensitivity | Information Ordering | Selective Attention | Category Flexibility | Inductive Reasoning | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | E-Mail | Contact With Others | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Spend Time Sitting | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Time Pressure | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Written Letters and Memos | Spend Time Making Repetitive Motions | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Billing and Posting Clerks | Bookkeeping, Accounting, and Auditing Clerks | Brokerage Clerks | Correspondence Clerks | Customer Service Representatives | Document Management Specialists | Executive Secretaries and Executive Administrative Assistants | File Clerks | First-Line Supervisors of Office and Administrative Support Workers | Human Resources Assistants, Except Payroll and Timekeeping | Interviewers, Except Eligibility and Loan | Legal Secretaries and Administrative Assistants | Management Analysts | Medical Records Specialists | Medical Secretaries and Administrative Assistants | Receptionists and Information Clerks | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Switchboard Operators, Including Answering Service | Word Processors and Typists</t>
+  </si>
+  <si>
+    <t>Perform duties too varied and diverse to be classified in any specific office clerical occupation, requiring knowledge of office systems and procedures. Clerical duties may be assigned in accordance with the office procedures of individual establishments and may include a combination of answering telephones, bookkeeping, typing or word processing, office machine operation, and filing.</t>
+  </si>
+  <si>
+    <t>Answer telephones, direct calls, and take messages. | Collect, count, and disburse money, do basic bookkeeping, and complete banking transactions. | Communicate with customers, employees, and other individuals to answer questions, disseminate or explain information, take orders, and address complaints. | Compile, copy, sort, and file records of office activities, business transactions, and other activities. | Complete and mail bills, contracts, policies, invoices, or checks. | Complete work schedules, manage calendars, and arrange appointments. | Compute, record, and proofread data and other information, such as records or reports. | Count, weigh, measure, or organize materials. | Deliver messages and run errands. | Inventory and order materials, supplies, and services. | Maintain and update filing, inventory, mailing, and database systems, either manually or using a computer. | Monitor and direct the work of lower-level clerks. | Open, sort, and route incoming mail, answer correspondence, and prepare outgoing mail. | Operate office machines, such as photocopiers and scanners, facsimile machines, voice mail systems, and personal computers. | Prepare meeting agendas, attend meetings, and record and transcribe minutes. | Process and prepare documents, such as business or government forms and expense reports. | Review files, records, and other documents to obtain information to respond to requests. | Train other staff members to perform work activities, such as using computer applications. | Troubleshoot problems involving office equipment, such as computer hardware and software. | Type, format, proofread, and edit correspondence and other documents, from notes or dictating machines, using computers or typewriters.</t>
+  </si>
+  <si>
+    <t>43-9071.00</t>
+  </si>
+  <si>
+    <t>Office Machine Operators, Except Computer</t>
+  </si>
+  <si>
+    <t>Copy Center Operator | Copy Machine Operator | Copy Technician | Graphics Production Specialist | Key Operator | Machine Operator | Printing Services Coordinator | Reprographics Technician</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Eko | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Windows | Microsoft Word | Multi-line optical character reader OCR software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Monitoring | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>English Language | Customer and Personal Service | Production and Processing | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Near Vision | Written Comprehension | Information Ordering | Oral Expression | Oral Comprehension | Arm-Hand Steadiness | Selective Attention | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>E-Mail | Time Pressure | Telephone Conversations | Contact With Others | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Camera and Photographic Equipment Repairers | Coin, Vending, and Amusement Machine Servicers and Repairers | Computer Numerically Controlled Tool Operators | Computer, Automated Teller, and Office Machine Repairers | Data Entry Keyers | File Clerks | Industrial Machinery Mechanics | Machine Feeders and Offbearers | Mail Clerks and Mail Machine Operators, Except Postal Service | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Photographic Process Workers and Processing Machine Operators | Postal Service Mail Sorters, Processors, and Processing Machine Operators | Prepress Technicians and Workers | Print Binding and Finishing Workers | Printing Press Operators | Production, Planning, and Expediting Clerks | Shipping, Receiving, and Inventory Clerks</t>
+  </si>
+  <si>
+    <t>Operate one or more of a variety of office machines, such as photocopying, photographic, and duplicating machines, or other office machines.</t>
+  </si>
+  <si>
+    <t>Clean and file master copies or plates. | Clean machines, perform minor repairs, and report major repair needs. | Complete records of production, including work volumes and outputs, materials used, and any backlogs. | Compute prices for services and receive payment, or provide supervisors with billing information. | Cut copies apart and write identifying information, such as page numbers or titles, on copies. | Deliver completed work. | File and store completed documents. | Load machines with materials such as blank paper or film. | Maintain stock of supplies, and requisition any needed items. | Monitor machine operation, and make adjustments as necessary to ensure proper operation. | Move heat units and clamping frames over screen beds to form Braille impressions on pages, raising frames to release individual copies. | Operate auxiliary machines such as collators, pad and tablet making machines, staplers, and paper punching, folding, cutting, and perforating machines. | Operate office machines such as high speed business photocopiers, readers, scanners, addressing machines, stencil-cutting machines, microfilm readers or printers, folding and inserting machines, bursters, and binder machines. | Place original copies in feed trays, feed originals into feed rolls, or position originals on tables beneath camera lenses. | Prepare and process papers for use in scanning, microfilming, and microfiche. | Read job orders to determine the type of work to be done, the quantities to be produced, and the materials needed. | Set up and adjust machines, regulating factors such as speed, ink flow, focus, and number of copies. | Sort, assemble, and proof completed work.</t>
+  </si>
+  <si>
+    <t>43-9081.00</t>
+  </si>
+  <si>
+    <t>Proofreaders and Copy Markers</t>
+  </si>
+  <si>
+    <t>Copy Editor | Copyholder | Editorial Assistant | News Copy Editor | Proofer | Proofreader | Typesetter</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Adobe After Effects | Adobe Captivate | Adobe Creative Cloud software | Adobe Dreamweaver | Adobe FrameMaker | Adobe Illustrator | Adobe InCopy | Adobe InDesign | Adobe Photoshop | After the Deadline | Apple Final Cut Pro | Apple iWork Keynote | AutoCrit Editing Wizard | Avid Technology Media Composer | Bugzilla | Elite Minds RightWriter | File transfer protocol FTP client software | FileMaker Pro | Grammarly Editor | HP Autonomy TeamSite | HubSpot software | InScribe | Intelligent Editing PerfectIt | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | Pro Writing Aid | QuarkXPress | Serenity Software Editor | Style guide databases | WhiteSmoke | WordPress | myWriterTools</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Writing | Speaking | Active Listening | Critical Thinking</t>
+  </si>
+  <si>
+    <t>English Language | Communications and Media | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Written Comprehension | Near Vision | Oral Comprehension | Written Expression | Oral Expression | Problem Sensitivity | Perceptual Speed | Deductive Reasoning | Speech Clarity | Speech Recognition | Information Ordering</t>
+  </si>
+  <si>
+    <t>Importance of Being Exact or Accurate | Spend Time Sitting | Indoors, Environmentally Controlled | Contact With Others | Time Pressure | E-Mail | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Telephone Conversations | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Archivists | Correspondence Clerks | Court Reporters and Simultaneous Captioners | Data Entry Keyers | Desktop Publishers | Document Management Specialists | Editors | File Clerks | Film and Video Editors | Librarians and Media Collections Specialists | Library Technicians | Medical Transcriptionists | News Analysts, Reporters, and Journalists | Office Machine Operators, Except Computer | Poets, Lyricists and Creative Writers | Social Science Research Assistants | Statistical Assistants | Technical Writers | Word Processors and Typists | Writers and Authors</t>
+  </si>
+  <si>
+    <t>Read transcript or proof type setup to detect and mark for correction any grammatical, typographical, or compositional errors. Excludes workers whose primary duty is editing copy. Includes proofreaders of braille.</t>
+  </si>
+  <si>
+    <t>Archive documents, conduct research, and read copy, using the internet and various computer programs. | Compare information or figures on one record against same data on other records, or with original copy, to detect errors. | Consult reference books or secure aid of readers to check references with rules of grammar and composition. | Consult with authors and editors regarding manuscript changes and suggestions. | Correct or record omissions, errors, or inconsistencies found. | Mark copy to indicate and correct errors in type, arrangement, grammar, punctuation, or spelling, using standard printers' marks. | Read corrected copies or proofs to ensure that all corrections have been made. | Read proof sheets aloud, calling out punctuation marks and spelling unusual words and proper names. | Route proofs with marked corrections to authors, editors, typists, or typesetters for correction or reprinting. | Typeset and measure dimensions, spacing, and positioning of page elements, such as copy and illustrations, to verify conformance to specifications, using printer's ruler or layout software. | Write original content, such as headlines, cutlines, captions, and cover copy.</t>
+  </si>
+  <si>
+    <t>43-9111.00</t>
+  </si>
+  <si>
+    <t>Statistical Assistants</t>
+  </si>
+  <si>
+    <t>Actuarial Analyst | Actuarial Assistant | Actuarial Technician | Administrative Analyst | Research Assistant | Statistical Clerk | Statistical Technician</t>
+  </si>
+  <si>
+    <t>A programming language APL | Avidian Technologies Prophet | Benfield ReMetrica | Bentley MicroStation | C# | C++ | Corel WordPerfect Office Suite | Data visualization software | Database software | GGY AXIS | Google Workspace software | Harvard Graphics | Hyland OnBase Enterprise Content Management | IBM Lotus 1-2-3 | IBM SPSS Statistics | Insightful S-PLUS | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic | Microsoft Visual Studio | Microsoft Word | Minitab | Oracle Java | Oracle PL/SQL | PolySystems Asset Delphi | Python | QSR International NVivo | R | SAP BusinessObjects Crystal Reports | SAS | STATISTICA | Software development tools | StataCorp Stata | Structured query language SQL | Systat Software SigmaStat | Tableau | The MathWorks MATLAB | Towers Perrin MoSes | Web browser software | Wolfram Research Mathematica | dBASE</t>
+  </si>
+  <si>
+    <t>Mathematics | Reading Comprehension | Critical Thinking | Active Learning | Writing | Active Listening | Speaking | Monitoring</t>
+  </si>
+  <si>
+    <t>English Language | Mathematics | Computers and Electronics | Customer and Personal Service | Education and Training | Administrative</t>
+  </si>
+  <si>
+    <t>Mathematical Reasoning | Written Comprehension | Number Facility | Oral Comprehension | Written Expression | Oral Expression | Inductive Reasoning | Information Ordering | Near Vision | Deductive Reasoning | Speech Clarity | Speech Recognition | Category Flexibility | Flexibility of Closure | Selective Attention | Problem Sensitivity | Fluency of Ideas | Perceptual Speed | Speed of Closure | Originality</t>
+  </si>
+  <si>
+    <t>E-Mail | Spend Time Sitting | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Telephone Conversations | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Contact With Others | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions | Time Pressure</t>
+  </si>
+  <si>
+    <t>Bioinformatics Technicians | Biostatisticians | Bookkeeping, Accounting, and Auditing Clerks | Business Intelligence Analysts | Clinical Data Managers | Computer Systems Analysts | Data Entry Keyers | Data Scientists | Database Administrators | Database Architects | Document Management Specialists | File Clerks | Financial Quantitative Analysts | Health Information Technologists and Medical Registrars | Management Analysts | Medical Records Specialists | Operations Research Analysts | Social Science Research Assistants | Statisticians | Survey Researchers</t>
+  </si>
+  <si>
+    <t>Compile and compute data according to statistical formulas for use in statistical studies. May perform actuarial computations and compile charts and graphs for use by actuaries. Includes actuarial clerks.</t>
+  </si>
+  <si>
+    <t>Check source data to verify completeness and accuracy. | Check survey responses for errors, such as the use of pens instead of pencils, and set aside response forms that cannot be used. | Code data prior to computer entry, using lists of codes. | Compile reports, charts, or graphs that describe and interpret findings of analyses. | Compile statistics from source materials, such as production or sales records, quality-control or test records, time sheets, or survey sheets. | Compute and analyze data, using statistical formulas and computers or calculators. | Discuss data presentation requirements with clients. | Enter data into computers for use in analyses or reports. | File data and related information, and maintain and update databases. | Interview people and keep track of their responses. | Organize paperwork, such as survey forms or reports, for distribution or analysis. | Participate in the publication of data or information. | Select statistical tests for analyzing data. | Send out surveys.</t>
+  </si>
+  <si>
+    <t>43-9199.00</t>
+  </si>
+  <si>
+    <t>Office and Administrative Support Workers, All Other</t>
+  </si>
+  <si>
+    <t>Administrative Aide | Administrative Assistant | Administrative Clerk | Administrative Support Specialist | Clerical Assistant | Office Assistant | Office Coordinator | Office Support Worker | Program Support Assistant | Staff Assistant</t>
+  </si>
+  <si>
+    <t>Administration and Management | English Language | Customer and Personal Service | Computers and Electronics | Mathematics | Economics and Accounting</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Office Clerks, General | Secretaries and Administrative Assistants, Except Legal, Medical, and Executive | Executive Secretaries and Executive Administrative Assistants | Medical Secretaries and Administrative Assistants | Legal Secretaries and Administrative Assistants | Data Entry Keyers | Word Processors and Typists | Receptionists and Information Clerks | Customer Service Representatives | File Clerks | Correspondence Clerks | Mail Clerks and Mail Machine Operators, Except Postal Service | Office Machine Operators, Except Computer | Proofreaders and Copy Markers | Statistical Assistants | Human Resources Assistants, Except Payroll and Timekeeping | Production, Planning, and Expediting Clerks | Shipping, Receiving, and Inventory Clerks | Information and Record Clerks, All Other | First-Line Supervisors of Office and Administrative Support Workers</t>
+  </si>
+  <si>
+    <t>All office and administrative support workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform office and administrative support duties not classified separately. | Answer telephones, greet visitors, and route inquiries to appropriate staff. | Prepare, format, and proofread correspondence, reports, and presentations. | Schedule appointments, meetings, and travel arrangements. | Maintain filing systems, databases, and office records. | Enter and verify data and generate routine reports. | Order and maintain inventories of office supplies and equipment. | Process incoming and outgoing mail, packages, and deliveries. | Operate and troubleshoot copiers, printers, and other office equipment. | Assist with budget tracking, expense reports, and purchase requests. | Coordinate meeting logistics, materials, and minutes. | Support projects by compiling information and tracking deliverables. | Maintain confidentiality of sensitive organizational information. | Train and assist coworkers on office procedures and systems.</t>
+  </si>
+  <si>
+    <t>45-1011.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Farming, Fishing, and Forestry Workers</t>
+  </si>
+  <si>
+    <t>Animal Research Facility Supervisor | Cattle Manager | Farm Supervisor | Fish Hatchery Manager | Harvesting Supervisor | Hatchery Manager | Logging Crew Foreman | Logging Supervisor | Pest Management Supervisor | Wildlife Manager</t>
+  </si>
+  <si>
+    <t>Atlassian Confluence | BCS Woodlands Software The Logger Tracker | Cattlesoft CattleMax | Database software | Employee scheduling software | Landmark Sales LOG-istics | Lion Edge Technologies Ranch Manager | Mapping software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Midwest MicroSystems Cow Sense | Payroll software | Sage 50 Accounting | TradeTec Computer Systems TallyWorks Logs | Valley Agricultural Software DairyCOMP 305 | Valley Agricultural Software Feed Watch | Web browser software | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Speaking | Reading Comprehension | Active Listening | Learning Strategies | Writing | Active Learning</t>
+  </si>
+  <si>
+    <t>Administration and Management | Production and Processing | Customer and Personal Service | English Language | Mechanical | Education and Training | Biology | Food Production | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Oral Expression | Speech Recognition | Near Vision | Speech Clarity | Far Vision | Category Flexibility | Information Ordering | Inductive Reasoning | Deductive Reasoning | Written Expression | Written Comprehension | Arm-Hand Steadiness | Control Precision | Manual Dexterity | Visualization | Perceptual Speed | Flexibility of Closure | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Outdoors, Exposed to All Weather Conditions | Freedom to Make Decisions | Contact With Others | In an Enclosed Vehicle or Operate Enclosed Equipment | Work Outcomes and Results of Other Workers | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Health and Safety of Other Workers | Importance of Being Exact or Accurate | Time Pressure | Exposed to Very Hot or Cold Temperatures | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | E-Mail | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Agricultural Technicians | Farmers, Ranchers, and Other Agricultural Managers | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Security Workers | Forest and Conservation Technicians | General and Operations Managers | Industrial Production Managers | Range Managers | Recycling Coordinators</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate the activities of agricultural, forestry, aquacultural, and related workers.</t>
+  </si>
+  <si>
+    <t>Assign tasks such as feeding and treatment of animals, and cleaning and maintenance of animal quarters. | Calculate or monitor budgets for maintenance or development of collections, grounds, or infrastructure. | Communicate with forestry personnel regarding forest harvesting or forest management plans, procedures, or schedules. | Confer with managers to determine production requirements, conditions of equipment and supplies, and work schedules. | Confer with managers to evaluate weather or soil conditions, to develop plans or procedures, or to discuss issues such as changes in fertilizers, herbicides, or cultivating techniques. | Coordinate dismantling, moving, and setting up equipment at new work sites. | Coordinate the selection and movement of logs from storage areas, according to transportation schedules or production requirements. | Direct or assist with the adjustment or repair of equipment or machinery. | Drive or operate farm machinery, such as trucks, tractors, or self-propelled harvesters, to transport workers or supplies or to cultivate or harvest fields. | Inspect buildings, fences, fields or ranges, supplies, and equipment to determine work to be performed. | Inspect crops, fields, or plant stock to determine conditions and need for cultivating, spraying, weeding, or harvesting. | Inspect facilities to determine maintenance needs. | Issue equipment, such as farm implements, machinery, ladders, or containers to workers, and collect equipment when work is complete. | Monitor operations to identify and solve problems, improve work methods, and ensure compliance with safety, company, and government regulations. | Monitor or oversee construction projects, such as horticultural buildings or irrigation systems. | Monitor workers to ensure that safety regulations are followed, warning or disciplining those who violate safety regulations. | Observe animals for signs of illness, injury, or unusual behavior, notifying veterinarians or managers as warranted. | Observe fish and beds or ponds to detect diseases, monitor fish growth, determine quality of fish, or determine completeness of harvesting. | Perform both supervisory and management functions, such as accounting, marketing, and personnel work. | Plan work schedules according to personnel and equipment availability. | Prepare and maintain time or payroll reports, as well as details of personnel actions, such as performance evaluations, hires, promotions, or disciplinary actions. | Read inventory records, customer orders, or shipping schedules to determine required activities. | Record the numbers and types of fish or shellfish reared, harvested, released, sold, and shipped. | Requisition or purchase supplies, such as insecticides, machine parts or lubricants, or tools. | Schedule work crews, equipment, or transportation for several different work locations. | Train workers in spawning, rearing, cultivating, and harvesting methods, and in the use of equipment. | Train workers in techniques such as planting, harvesting, weeding, or insect identification and in the use of safety measures. | Train workers in tree felling or bucking, operation of tractors or loading machines, yarding or loading techniques, or safety regulations. | Transport or arrange for transport of animals, equipment, food, animal feed, and other supplies to and from work sites. | Treat animal illnesses or injuries, following experience or instructions of veterinarians.</t>
+  </si>
+  <si>
+    <t>45-2011.00</t>
+  </si>
+  <si>
+    <t>Agricultural Inspectors</t>
+  </si>
+  <si>
+    <t>Brand Inspector | Consumer Safety Inspector (CSI) | Food Inspector | Food Safety and Inspection Service Inspector (FSIS Inspector) | Food Sanitarian | Grain Inspector | Inspector | Seed and Fertilizer Specialist | Shipping Point Inspector</t>
+  </si>
+  <si>
+    <t>Image processing software | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Operational databases</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Monitoring | Critical Thinking | Speaking | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management | Law and Government | Administrative | Public Safety and Security | Mathematics | English Language</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Comprehension | Deductive Reasoning | Inductive Reasoning | Near Vision | Oral Expression | Written Comprehension | Flexibility of Closure | Speech Clarity | Far Vision | Perceptual Speed | Speech Recognition | Speed of Closure | Category Flexibility | Information Ordering | Written Expression | Auditory Attention | Selective Attention</t>
+  </si>
+  <si>
+    <t>Importance of Being Exact or Accurate | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Deal With External Customers or the Public in General | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Exposed to Contaminants | Telephone Conversations | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Outdoors, Exposed to All Weather Conditions | Time Pressure | Indoors, Not Environmentally Controlled | Exposed to Very Hot or Cold Temperatures | Physical Proximity | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Coordinate or Lead Others in Accomplishing Work Activities | E-Mail</t>
+  </si>
+  <si>
+    <t>Agricultural Technicians | Aviation Inspectors | Construction and Building Inspectors | Environmental Compliance Inspectors | Environmental Science and Protection Technicians, Including Health | First-Line Supervisors of Farming, Fishing, and Forestry Workers | Food Science Technicians | Food Scientists and Technologists | Government Property Inspectors and Investigators | Graders and Sorters, Agricultural Products | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Industrial Production Managers | Inspectors, Testers, Sorters, Samplers, and Weighers | Occupational Health and Safety Specialists | Occupational Health and Safety Technicians | Quality Control Analysts | Quality Control Systems Managers | Transportation Inspectors | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation | Weighers, Measurers, Checkers, and Samplers, Recordkeeping</t>
+  </si>
+  <si>
+    <t>Inspect agricultural commodities, processing equipment, and facilities, and fish and logging operations, to ensure compliance with regulations and laws governing health, quality, and safety.</t>
+  </si>
+  <si>
+    <t>Collect samples from animals, plants, or products and route them to laboratories for microbiological assessment, ingredient verification, or other testing. | Compare product recipes with government-approved formulas or recipes to determine acceptability. | Examine, weigh, and measure commodities, such as poultry, eggs, meat, or seafood to certify qualities, grades, and weights. | Inspect agricultural commodities or related operations, as well as fish or logging operations, for compliance with laws and regulations governing health, quality, and safety. | Inspect food products and processing procedures to determine whether products are safe to eat. | Inspect or test horticultural products or livestock to detect harmful diseases, chemical residues, or infestations and to determine the quality of products or animals. | Inspect the cleanliness and practices of establishment employees. | Interpret and enforce government acts and regulations and explain required standards to agricultural workers. | Label and seal graded products and issue official grading certificates. | Monitor the grading performed by company employees to verify conformance to standards. | Monitor the operations and sanitary conditions of slaughtering or meat processing plants. | Provide consultative services in areas such as equipment or product evaluation, plant construction or layout, or food safety systems. | Take emergency actions, such as closing production facilities, if product safety is compromised. | Testify in legal proceedings. | Verify that transportation and handling procedures meet regulatory requirements. | Write reports of findings and recommendations and advise farmers, growers, or processors of corrective action to be taken.</t>
+  </si>
+  <si>
+    <t>45-2021.00</t>
+  </si>
+  <si>
+    <t>Animal Breeders</t>
+  </si>
+  <si>
+    <t>Animal Technician | Artificial Insemination Technician (AI Technician) | Artificial Inseminator | Breeder | Dog Breeder | Large Herd Specialist</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Adobe Creative Cloud software | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Breedtrak | Email software | KinTraks | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Questionmark Perception | Respondus | Reudink Software ZooEasy | VSN International GenStat | Winners Programs BirdStud | Winners Programs Uni-Stud</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Learning | Science | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Sales and Marketing | Administration and Management | Biology | Mathematics | Administrative</t>
+  </si>
+  <si>
+    <t>Near Vision | Category Flexibility | Deductive Reasoning | Problem Sensitivity | Speech Clarity | Far Vision | Trunk Strength | Static Strength | Multilimb Coordination | Finger Dexterity | Arm-Hand Steadiness | Information Ordering | Inductive Reasoning | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Outdoors, Exposed to All Weather Conditions | Consequence of Error | Outdoors, Under Cover</t>
+  </si>
+  <si>
+    <t>Agricultural Inspectors | Agricultural Technicians | Animal Caretakers | Animal Control Workers | Animal Scientists | Animal Trainers | Buyers and Purchasing Agents, Farm Products | Farmers, Ranchers, and Other Agricultural Managers | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | Farmworkers, Farm, Ranch, and Aquacultural Animals | First-Line Supervisors of Farming, Fishing, and Forestry Workers | Fishing and Hunting Workers | Food Scientists and Technologists | Graders and Sorters, Agricultural Products | Meat, Poultry, and Fish Cutters and Trimmers | Slaughterers and Meat Packers | Soil and Plant Scientists | Veterinarians | Veterinary Assistants and Laboratory Animal Caretakers | Veterinary Technologists and Technicians</t>
+  </si>
+  <si>
+    <t>Select and breed animals according to their genealogy, characteristics, and offspring. May require knowledge of artificial insemination techniques and equipment use. May involve keeping records on heats, birth intervals, or pedigree.</t>
+  </si>
+  <si>
+    <t>Adjust controls to maintain specific building temperatures required for animals' health and safety. | Arrange for sale of animals and eggs to hospitals, research centers, pet shops, and food processing plants. | Bathe and groom animals. | Brand, tattoo, or tag animals to allow animal identification. | Build hutches, pens, and fenced yards. | Clip or shear hair on animals. | Examine animals to detect symptoms of illness or injury. | Examine semen microscopically to assess and record density and motility of gametes, and dilute semen with prescribed diluents, according to formulas. | Exercise animals to keep them in healthy condition. | Exhibit animals at shows. | Feed and water animals, and clean and disinfect pens, cages, yards, and hutches. | Inject prepared animal semen into female animals for breeding purposes, by inserting nozzle of syringe into vagina and depressing syringe plunger. | Maintain logs of semen specimens used and animals bred. | Measure specified amounts of semen into calibrated syringes, and insert syringes into inseminating guns. | Observe animals in heat to detect approach of estrus and exercise animals to induce or hasten estrus, if necessary. | Package and label semen to be used for artificial insemination, recording information such as the date, source, quality, and concentration. | Place vaccines in drinking water, inject vaccines, or dust air with vaccine powder to protect animals from diseases. | Purchase and stock supplies of feed and medicines. | Record animal characteristics such as weights, growth patterns, and diets. | Select animals to be bred, and semen specimens to be used, according to knowledge of animals, genealogies, traits, and desired offspring characteristics. | Treat minor injuries and ailments and contact veterinarians to obtain treatment for animals with serious illnesses or injuries.</t>
+  </si>
+  <si>
+    <t>45-2041.00</t>
+  </si>
+  <si>
+    <t>Graders and Sorters, Agricultural Products</t>
+  </si>
+  <si>
+    <t>Agriculture Laborer | Apple Sorter | Corn Lab Technician | Distribution Technician | Egg Grader | Egg Worker | Grader | Potato Grader | Potato Sorter | Sorter</t>
+  </si>
+  <si>
+    <t>Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Production and Processing | English Language</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Near Vision | Category Flexibility | Finger Dexterity | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Physical Proximity | Indoors, Environmentally Controlled | Time Pressure | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Pace Determined by Speed of Equipment | Work With or Contribute to a Work Group or Team | Contact With Others | Importance of Being Exact or Accurate</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Agricultural Inspectors | Bakers | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food Science Technicians | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Laborers and Freight, Stock, and Material Movers, Hand | Log Graders and Scalers | Machine Feeders and Offbearers | Meat, Poultry, and Fish Cutters and Trimmers | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Weighers, Measurers, Checkers, and Samplers, Recordkeeping</t>
+  </si>
+  <si>
+    <t>Grade, sort, or classify unprocessed food and other agricultural products by size, weight, color, or condition.</t>
+  </si>
+  <si>
+    <t>Discard inferior or defective products or foreign matter, and place acceptable products in containers for further processing. | Grade and sort products according to factors such as color, species, length, width, appearance, feel, smell, and quality to ensure correct processing and usage. | Place products in containers according to grade and mark grades on containers. | Record grade or identification numbers on tags or on shipping, receiving, or sales sheets. | Weigh products or estimate their weight, visually or by feel.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +1964,1761 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I11" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" t="s">
+        <v>137</v>
+      </c>
+      <c r="H13" t="s">
+        <v>138</v>
+      </c>
+      <c r="I13" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G14" t="s">
+        <v>148</v>
+      </c>
+      <c r="H14" t="s">
+        <v>149</v>
+      </c>
+      <c r="I14" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" t="s">
+        <v>151</v>
+      </c>
+      <c r="K14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" t="s">
+        <v>159</v>
+      </c>
+      <c r="H15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I15" t="s">
+        <v>161</v>
+      </c>
+      <c r="J15" t="s">
+        <v>162</v>
+      </c>
+      <c r="K15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" t="s">
+        <v>167</v>
+      </c>
+      <c r="E16" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" t="s">
+        <v>169</v>
+      </c>
+      <c r="G16" t="s">
+        <v>170</v>
+      </c>
+      <c r="H16" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" t="s">
+        <v>172</v>
+      </c>
+      <c r="J16" t="s">
+        <v>173</v>
+      </c>
+      <c r="K16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" t="s">
+        <v>180</v>
+      </c>
+      <c r="G17" t="s">
+        <v>181</v>
+      </c>
+      <c r="H17" t="s">
+        <v>182</v>
+      </c>
+      <c r="I17" t="s">
+        <v>183</v>
+      </c>
+      <c r="J17" t="s">
+        <v>184</v>
+      </c>
+      <c r="K17" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" t="s">
+        <v>188</v>
+      </c>
+      <c r="D18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F18" t="s">
+        <v>191</v>
+      </c>
+      <c r="G18" t="s">
+        <v>192</v>
+      </c>
+      <c r="H18" t="s">
+        <v>193</v>
+      </c>
+      <c r="I18" t="s">
+        <v>194</v>
+      </c>
+      <c r="J18" t="s">
+        <v>195</v>
+      </c>
+      <c r="K18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" t="s">
+        <v>201</v>
+      </c>
+      <c r="F19" t="s">
+        <v>202</v>
+      </c>
+      <c r="G19" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" t="s">
+        <v>204</v>
+      </c>
+      <c r="I19" t="s">
+        <v>205</v>
+      </c>
+      <c r="J19" t="s">
+        <v>206</v>
+      </c>
+      <c r="K19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" t="s">
+        <v>212</v>
+      </c>
+      <c r="G20" t="s">
+        <v>213</v>
+      </c>
+      <c r="H20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" t="s">
+        <v>214</v>
+      </c>
+      <c r="J20" t="s">
+        <v>215</v>
+      </c>
+      <c r="K20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C21" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" t="s">
+        <v>221</v>
+      </c>
+      <c r="F21" t="s">
+        <v>222</v>
+      </c>
+      <c r="G21" t="s">
+        <v>223</v>
+      </c>
+      <c r="H21" t="s">
+        <v>224</v>
+      </c>
+      <c r="I21" t="s">
+        <v>225</v>
+      </c>
+      <c r="J21" t="s">
+        <v>226</v>
+      </c>
+      <c r="K21" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>228</v>
+      </c>
+      <c r="B22" t="s">
+        <v>229</v>
+      </c>
+      <c r="C22" t="s">
+        <v>230</v>
+      </c>
+      <c r="D22" t="s">
+        <v>231</v>
+      </c>
+      <c r="E22" t="s">
+        <v>232</v>
+      </c>
+      <c r="F22" t="s">
+        <v>233</v>
+      </c>
+      <c r="G22" t="s">
+        <v>234</v>
+      </c>
+      <c r="H22" t="s">
+        <v>235</v>
+      </c>
+      <c r="I22" t="s">
+        <v>236</v>
+      </c>
+      <c r="J22" t="s">
+        <v>237</v>
+      </c>
+      <c r="K22" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>239</v>
+      </c>
+      <c r="B23" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" t="s">
+        <v>243</v>
+      </c>
+      <c r="F23" t="s">
+        <v>244</v>
+      </c>
+      <c r="G23" t="s">
+        <v>245</v>
+      </c>
+      <c r="H23" t="s">
+        <v>246</v>
+      </c>
+      <c r="I23" t="s">
+        <v>247</v>
+      </c>
+      <c r="J23" t="s">
+        <v>248</v>
+      </c>
+      <c r="K23" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>250</v>
+      </c>
+      <c r="B24" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" t="s">
+        <v>252</v>
+      </c>
+      <c r="D24" t="s">
+        <v>253</v>
+      </c>
+      <c r="E24" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24" t="s">
+        <v>255</v>
+      </c>
+      <c r="G24" t="s">
+        <v>256</v>
+      </c>
+      <c r="H24" t="s">
+        <v>257</v>
+      </c>
+      <c r="I24" t="s">
+        <v>258</v>
+      </c>
+      <c r="J24" t="s">
+        <v>259</v>
+      </c>
+      <c r="K24" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>261</v>
+      </c>
+      <c r="B25" t="s">
+        <v>262</v>
+      </c>
+      <c r="C25" t="s">
+        <v>263</v>
+      </c>
+      <c r="D25" t="s">
+        <v>264</v>
+      </c>
+      <c r="E25" t="s">
+        <v>265</v>
+      </c>
+      <c r="F25" t="s">
+        <v>266</v>
+      </c>
+      <c r="G25" t="s">
+        <v>267</v>
+      </c>
+      <c r="H25" t="s">
+        <v>268</v>
+      </c>
+      <c r="I25" t="s">
+        <v>269</v>
+      </c>
+      <c r="J25" t="s">
+        <v>270</v>
+      </c>
+      <c r="K25" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>272</v>
+      </c>
+      <c r="B26" t="s">
+        <v>273</v>
+      </c>
+      <c r="C26" t="s">
+        <v>274</v>
+      </c>
+      <c r="D26" t="s">
+        <v>275</v>
+      </c>
+      <c r="E26" t="s">
+        <v>276</v>
+      </c>
+      <c r="F26" t="s">
+        <v>277</v>
+      </c>
+      <c r="G26" t="s">
+        <v>278</v>
+      </c>
+      <c r="H26" t="s">
+        <v>279</v>
+      </c>
+      <c r="I26" t="s">
+        <v>280</v>
+      </c>
+      <c r="J26" t="s">
+        <v>281</v>
+      </c>
+      <c r="K26" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>283</v>
+      </c>
+      <c r="B27" t="s">
+        <v>284</v>
+      </c>
+      <c r="C27" t="s">
+        <v>285</v>
+      </c>
+      <c r="D27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E27" t="s">
+        <v>287</v>
+      </c>
+      <c r="F27" t="s">
+        <v>288</v>
+      </c>
+      <c r="G27" t="s">
+        <v>289</v>
+      </c>
+      <c r="H27" t="s">
+        <v>290</v>
+      </c>
+      <c r="I27" t="s">
+        <v>291</v>
+      </c>
+      <c r="J27" t="s">
+        <v>292</v>
+      </c>
+      <c r="K27" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>294</v>
+      </c>
+      <c r="B28" t="s">
+        <v>295</v>
+      </c>
+      <c r="C28" t="s">
+        <v>296</v>
+      </c>
+      <c r="D28" t="s">
+        <v>297</v>
+      </c>
+      <c r="E28" t="s">
+        <v>298</v>
+      </c>
+      <c r="F28" t="s">
+        <v>299</v>
+      </c>
+      <c r="G28" t="s">
+        <v>300</v>
+      </c>
+      <c r="H28" t="s">
+        <v>301</v>
+      </c>
+      <c r="I28" t="s">
+        <v>302</v>
+      </c>
+      <c r="J28" t="s">
+        <v>303</v>
+      </c>
+      <c r="K28" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>305</v>
+      </c>
+      <c r="B29" t="s">
+        <v>306</v>
+      </c>
+      <c r="C29" t="s">
+        <v>307</v>
+      </c>
+      <c r="D29" t="s">
+        <v>308</v>
+      </c>
+      <c r="E29" t="s">
+        <v>309</v>
+      </c>
+      <c r="F29" t="s">
+        <v>310</v>
+      </c>
+      <c r="G29" t="s">
+        <v>311</v>
+      </c>
+      <c r="H29" t="s">
+        <v>312</v>
+      </c>
+      <c r="I29" t="s">
+        <v>313</v>
+      </c>
+      <c r="J29" t="s">
+        <v>314</v>
+      </c>
+      <c r="K29" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>316</v>
+      </c>
+      <c r="B30" t="s">
+        <v>317</v>
+      </c>
+      <c r="C30" t="s">
+        <v>318</v>
+      </c>
+      <c r="D30" t="s">
+        <v>319</v>
+      </c>
+      <c r="E30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" t="s">
+        <v>320</v>
+      </c>
+      <c r="G30" t="s">
+        <v>321</v>
+      </c>
+      <c r="H30" t="s">
+        <v>322</v>
+      </c>
+      <c r="I30" t="s">
+        <v>323</v>
+      </c>
+      <c r="J30" t="s">
+        <v>324</v>
+      </c>
+      <c r="K30" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>326</v>
+      </c>
+      <c r="B31" t="s">
+        <v>327</v>
+      </c>
+      <c r="C31" t="s">
+        <v>328</v>
+      </c>
+      <c r="D31" t="s">
+        <v>329</v>
+      </c>
+      <c r="E31" t="s">
+        <v>330</v>
+      </c>
+      <c r="F31" t="s">
+        <v>331</v>
+      </c>
+      <c r="G31" t="s">
+        <v>332</v>
+      </c>
+      <c r="H31" t="s">
+        <v>333</v>
+      </c>
+      <c r="I31" t="s">
+        <v>334</v>
+      </c>
+      <c r="J31" t="s">
+        <v>335</v>
+      </c>
+      <c r="K31" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>337</v>
+      </c>
+      <c r="B32" t="s">
+        <v>338</v>
+      </c>
+      <c r="C32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D32" t="s">
+        <v>340</v>
+      </c>
+      <c r="E32" t="s">
+        <v>341</v>
+      </c>
+      <c r="F32" t="s">
+        <v>342</v>
+      </c>
+      <c r="G32" t="s">
+        <v>343</v>
+      </c>
+      <c r="H32" t="s">
+        <v>344</v>
+      </c>
+      <c r="I32" t="s">
+        <v>345</v>
+      </c>
+      <c r="J32" t="s">
+        <v>346</v>
+      </c>
+      <c r="K32" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>348</v>
+      </c>
+      <c r="B33" t="s">
+        <v>349</v>
+      </c>
+      <c r="C33" t="s">
+        <v>350</v>
+      </c>
+      <c r="D33" t="s">
+        <v>351</v>
+      </c>
+      <c r="E33" t="s">
+        <v>352</v>
+      </c>
+      <c r="F33" t="s">
+        <v>353</v>
+      </c>
+      <c r="G33" t="s">
+        <v>354</v>
+      </c>
+      <c r="H33" t="s">
+        <v>355</v>
+      </c>
+      <c r="I33" t="s">
+        <v>356</v>
+      </c>
+      <c r="J33" t="s">
+        <v>357</v>
+      </c>
+      <c r="K33" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>359</v>
+      </c>
+      <c r="B34" t="s">
+        <v>360</v>
+      </c>
+      <c r="C34" t="s">
+        <v>361</v>
+      </c>
+      <c r="D34" t="s">
+        <v>362</v>
+      </c>
+      <c r="E34" t="s">
+        <v>363</v>
+      </c>
+      <c r="F34" t="s">
+        <v>364</v>
+      </c>
+      <c r="G34" t="s">
+        <v>365</v>
+      </c>
+      <c r="H34" t="s">
+        <v>366</v>
+      </c>
+      <c r="I34" t="s">
+        <v>367</v>
+      </c>
+      <c r="J34" t="s">
+        <v>368</v>
+      </c>
+      <c r="K34" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>370</v>
+      </c>
+      <c r="B35" t="s">
+        <v>371</v>
+      </c>
+      <c r="C35" t="s">
+        <v>372</v>
+      </c>
+      <c r="D35" t="s">
+        <v>373</v>
+      </c>
+      <c r="E35" t="s">
+        <v>374</v>
+      </c>
+      <c r="F35" t="s">
+        <v>375</v>
+      </c>
+      <c r="G35" t="s">
+        <v>376</v>
+      </c>
+      <c r="H35" t="s">
+        <v>377</v>
+      </c>
+      <c r="I35" t="s">
+        <v>378</v>
+      </c>
+      <c r="J35" t="s">
+        <v>379</v>
+      </c>
+      <c r="K35" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>381</v>
+      </c>
+      <c r="B36" t="s">
+        <v>382</v>
+      </c>
+      <c r="C36" t="s">
+        <v>383</v>
+      </c>
+      <c r="D36" t="s">
+        <v>384</v>
+      </c>
+      <c r="E36" t="s">
+        <v>385</v>
+      </c>
+      <c r="F36" t="s">
+        <v>386</v>
+      </c>
+      <c r="G36" t="s">
+        <v>387</v>
+      </c>
+      <c r="H36" t="s">
+        <v>388</v>
+      </c>
+      <c r="I36" t="s">
+        <v>389</v>
+      </c>
+      <c r="J36" t="s">
+        <v>390</v>
+      </c>
+      <c r="K36" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>392</v>
+      </c>
+      <c r="B37" t="s">
+        <v>393</v>
+      </c>
+      <c r="C37" t="s">
+        <v>394</v>
+      </c>
+      <c r="D37" t="s">
+        <v>395</v>
+      </c>
+      <c r="E37" t="s">
+        <v>396</v>
+      </c>
+      <c r="F37" t="s">
+        <v>397</v>
+      </c>
+      <c r="G37" t="s">
+        <v>398</v>
+      </c>
+      <c r="H37" t="s">
+        <v>399</v>
+      </c>
+      <c r="I37" t="s">
+        <v>400</v>
+      </c>
+      <c r="J37" t="s">
+        <v>401</v>
+      </c>
+      <c r="K37" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>403</v>
+      </c>
+      <c r="B38" t="s">
+        <v>404</v>
+      </c>
+      <c r="C38" t="s">
+        <v>405</v>
+      </c>
+      <c r="D38" t="s">
+        <v>406</v>
+      </c>
+      <c r="E38" t="s">
+        <v>407</v>
+      </c>
+      <c r="F38" t="s">
+        <v>408</v>
+      </c>
+      <c r="G38" t="s">
+        <v>409</v>
+      </c>
+      <c r="H38" t="s">
+        <v>410</v>
+      </c>
+      <c r="I38" t="s">
+        <v>411</v>
+      </c>
+      <c r="J38" t="s">
+        <v>412</v>
+      </c>
+      <c r="K38" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>414</v>
+      </c>
+      <c r="B39" t="s">
+        <v>415</v>
+      </c>
+      <c r="C39" t="s">
+        <v>416</v>
+      </c>
+      <c r="D39" t="s">
+        <v>417</v>
+      </c>
+      <c r="E39" t="s">
+        <v>418</v>
+      </c>
+      <c r="F39" t="s">
+        <v>419</v>
+      </c>
+      <c r="G39" t="s">
+        <v>420</v>
+      </c>
+      <c r="H39" t="s">
+        <v>421</v>
+      </c>
+      <c r="I39" t="s">
+        <v>422</v>
+      </c>
+      <c r="J39" t="s">
+        <v>423</v>
+      </c>
+      <c r="K39" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>425</v>
+      </c>
+      <c r="B40" t="s">
+        <v>426</v>
+      </c>
+      <c r="C40" t="s">
+        <v>427</v>
+      </c>
+      <c r="D40" t="s">
+        <v>428</v>
+      </c>
+      <c r="E40" t="s">
+        <v>70</v>
+      </c>
+      <c r="F40" t="s">
+        <v>191</v>
+      </c>
+      <c r="G40" t="s">
+        <v>429</v>
+      </c>
+      <c r="H40" t="s">
+        <v>430</v>
+      </c>
+      <c r="I40" t="s">
+        <v>431</v>
+      </c>
+      <c r="J40" t="s">
+        <v>432</v>
+      </c>
+      <c r="K40" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>434</v>
+      </c>
+      <c r="B41" t="s">
+        <v>435</v>
+      </c>
+      <c r="C41" t="s">
+        <v>436</v>
+      </c>
+      <c r="D41" t="s">
+        <v>437</v>
+      </c>
+      <c r="E41" t="s">
+        <v>309</v>
+      </c>
+      <c r="F41" t="s">
+        <v>438</v>
+      </c>
+      <c r="G41" t="s">
+        <v>439</v>
+      </c>
+      <c r="H41" t="s">
+        <v>440</v>
+      </c>
+      <c r="I41" t="s">
+        <v>441</v>
+      </c>
+      <c r="J41" t="s">
+        <v>442</v>
+      </c>
+      <c r="K41" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>444</v>
+      </c>
+      <c r="B42" t="s">
+        <v>445</v>
+      </c>
+      <c r="C42" t="s">
+        <v>446</v>
+      </c>
+      <c r="D42" t="s">
+        <v>447</v>
+      </c>
+      <c r="E42" t="s">
+        <v>448</v>
+      </c>
+      <c r="F42" t="s">
+        <v>449</v>
+      </c>
+      <c r="G42" t="s">
+        <v>450</v>
+      </c>
+      <c r="H42" t="s">
+        <v>451</v>
+      </c>
+      <c r="I42" t="s">
+        <v>452</v>
+      </c>
+      <c r="J42" t="s">
+        <v>453</v>
+      </c>
+      <c r="K42" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>455</v>
+      </c>
+      <c r="B43" t="s">
+        <v>456</v>
+      </c>
+      <c r="C43" t="s">
+        <v>457</v>
+      </c>
+      <c r="D43" t="s">
+        <v>458</v>
+      </c>
+      <c r="E43" t="s">
+        <v>459</v>
+      </c>
+      <c r="F43" t="s">
+        <v>460</v>
+      </c>
+      <c r="G43" t="s">
+        <v>461</v>
+      </c>
+      <c r="H43" t="s">
+        <v>462</v>
+      </c>
+      <c r="I43" t="s">
+        <v>463</v>
+      </c>
+      <c r="J43" t="s">
+        <v>464</v>
+      </c>
+      <c r="K43" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>466</v>
+      </c>
+      <c r="B44" t="s">
+        <v>467</v>
+      </c>
+      <c r="C44" t="s">
+        <v>468</v>
+      </c>
+      <c r="D44" t="s">
+        <v>469</v>
+      </c>
+      <c r="E44" t="s">
+        <v>470</v>
+      </c>
+      <c r="F44" t="s">
+        <v>471</v>
+      </c>
+      <c r="G44" t="s">
+        <v>472</v>
+      </c>
+      <c r="H44" t="s">
+        <v>473</v>
+      </c>
+      <c r="I44" t="s">
+        <v>474</v>
+      </c>
+      <c r="J44" t="s">
+        <v>475</v>
+      </c>
+      <c r="K44" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>477</v>
+      </c>
+      <c r="B45" t="s">
+        <v>478</v>
+      </c>
+      <c r="C45" t="s">
+        <v>479</v>
+      </c>
+      <c r="D45" t="s">
+        <v>480</v>
+      </c>
+      <c r="E45" t="s">
+        <v>481</v>
+      </c>
+      <c r="F45" t="s">
+        <v>482</v>
+      </c>
+      <c r="G45" t="s">
+        <v>483</v>
+      </c>
+      <c r="H45" t="s">
+        <v>484</v>
+      </c>
+      <c r="I45" t="s">
+        <v>485</v>
+      </c>
+      <c r="J45" t="s">
+        <v>486</v>
+      </c>
+      <c r="K45" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>488</v>
+      </c>
+      <c r="B46" t="s">
+        <v>489</v>
+      </c>
+      <c r="C46" t="s">
+        <v>490</v>
+      </c>
+      <c r="D46" t="s">
+        <v>211</v>
+      </c>
+      <c r="E46" t="s">
+        <v>26</v>
+      </c>
+      <c r="F46" t="s">
+        <v>491</v>
+      </c>
+      <c r="G46" t="s">
+        <v>492</v>
+      </c>
+      <c r="H46" t="s">
+        <v>493</v>
+      </c>
+      <c r="I46" t="s">
+        <v>494</v>
+      </c>
+      <c r="J46" t="s">
+        <v>495</v>
+      </c>
+      <c r="K46" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>497</v>
+      </c>
+      <c r="B47" t="s">
+        <v>498</v>
+      </c>
+      <c r="C47" t="s">
+        <v>499</v>
+      </c>
+      <c r="D47" t="s">
+        <v>500</v>
+      </c>
+      <c r="E47" t="s">
+        <v>501</v>
+      </c>
+      <c r="F47" t="s">
+        <v>502</v>
+      </c>
+      <c r="G47" t="s">
+        <v>503</v>
+      </c>
+      <c r="H47" t="s">
+        <v>504</v>
+      </c>
+      <c r="I47" t="s">
+        <v>505</v>
+      </c>
+      <c r="J47" t="s">
+        <v>506</v>
+      </c>
+      <c r="K47" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>508</v>
+      </c>
+      <c r="B48" t="s">
+        <v>509</v>
+      </c>
+      <c r="C48" t="s">
+        <v>510</v>
+      </c>
+      <c r="D48" t="s">
+        <v>511</v>
+      </c>
+      <c r="E48" t="s">
+        <v>512</v>
+      </c>
+      <c r="F48" t="s">
+        <v>513</v>
+      </c>
+      <c r="G48" t="s">
+        <v>514</v>
+      </c>
+      <c r="H48" t="s">
+        <v>515</v>
+      </c>
+      <c r="I48" t="s">
+        <v>516</v>
+      </c>
+      <c r="J48" t="s">
+        <v>517</v>
+      </c>
+      <c r="K48" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>519</v>
+      </c>
+      <c r="B49" t="s">
+        <v>520</v>
+      </c>
+      <c r="C49" t="s">
+        <v>521</v>
+      </c>
+      <c r="D49" t="s">
+        <v>522</v>
+      </c>
+      <c r="E49" t="s">
+        <v>523</v>
+      </c>
+      <c r="F49" t="s">
+        <v>524</v>
+      </c>
+      <c r="G49" t="s">
+        <v>525</v>
+      </c>
+      <c r="H49" t="s">
+        <v>526</v>
+      </c>
+      <c r="I49" t="s">
+        <v>527</v>
+      </c>
+      <c r="J49" t="s">
+        <v>528</v>
+      </c>
+      <c r="K49" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>530</v>
+      </c>
+      <c r="B50" t="s">
+        <v>531</v>
+      </c>
+      <c r="C50" t="s">
+        <v>532</v>
+      </c>
+      <c r="D50" t="s">
+        <v>533</v>
+      </c>
+      <c r="E50" t="s">
+        <v>534</v>
+      </c>
+      <c r="F50" t="s">
+        <v>535</v>
+      </c>
+      <c r="G50" t="s">
+        <v>536</v>
+      </c>
+      <c r="H50" t="s">
+        <v>537</v>
+      </c>
+      <c r="I50" t="s">
+        <v>538</v>
+      </c>
+      <c r="J50" t="s">
+        <v>539</v>
+      </c>
+      <c r="K50" t="s">
+        <v>540</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>